--- a/documentos/2026-10-20 RQM Complemento de Modúlo de consulta de logs/T29 - Casos de prueba.xlsx
+++ b/documentos/2026-10-20 RQM Complemento de Modúlo de consulta de logs/T29 - Casos de prueba.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Resumen" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Casos de prueba'!$A$1:$M$51</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Casos de prueba'!$A$1:$M$59</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="429">
   <si>
     <t xml:space="preserve">RQM Complemento módulo de Consulta de Logs + Marca de Oferta – T29 Casos de prueba</t>
   </si>
@@ -999,6 +999,150 @@
   </si>
   <si>
     <t xml:space="preserve">Pendiente desde T23.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E4-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BD - script 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ejecutar 20 dos veces.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sin errores; objetos creados una vez.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECT name FROM sys.objects WHERE name LIKE '%INTERNAL_REFERENCE%';</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E4-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3/C5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consecutivos - validaciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modificación de artículos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generar sin código; con espacios; con 7 caracteres; cantidad 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mensajes de validación; no genera.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E4-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consecutivos - código nuevo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Código sin artículos ni generados (ej. ZZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generar 3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genera ZZ-001, ZZ-002, ZZ-003.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECT * FROM INTERNAL_REFERENCE_CONSECUTIVES WHERE CODE = 'ZZ';</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E4-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consecutivos - código con artículos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Código con artículos (ej. el mayor es MU-025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generar 2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genera MU-026 y MU-027 (por encima del mayor usado).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECT MAX(INTERNAL_REFERENCE) FROM items WHERE INTERNAL_REFERENCE LIKE 'MU-[0-9][0-9][0-9]';</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E4-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consecutivos - Consultar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generados del caso anterior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crear un artículo con MU-026; Consultar MU.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo aparece MU-027.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E4-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consecutivos - minúsculas y prefijos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consultar 'mu'; generar para MUX.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'mu' = MU; MUX no se mezcla con MU.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E4-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consecutivos - concurrencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dos usuarios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dos sesiones generan para el mismo código al mismo tiempo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sin consecutivos duplicados (PK código+número).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECT CODE, CONSECUTIVE, COUNT(*) FROM INTERNAL_REFERENCE_CONSECUTIVES GROUP BY CODE, CONSECUTIVE HAVING COUNT(*) &gt; 1; -- 0 filas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E4-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pruebas unitarias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desarrollo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dotnet test sobre Aldebaran.Application.Services.Tests.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todas en verde.</t>
   </si>
   <si>
     <t xml:space="preserve">Área</t>
@@ -1740,7 +1884,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -3448,9 +3592,273 @@
       <c r="L51" s="6"/>
       <c r="M51" s="6"/>
     </row>
+    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
+      <c r="M52" s="6"/>
+    </row>
+    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J53" s="6"/>
+      <c r="K53" s="6"/>
+      <c r="L53" s="6"/>
+      <c r="M53" s="6"/>
+    </row>
+    <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="6"/>
+      <c r="M54" s="6"/>
+    </row>
+    <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="J55" s="6"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="6"/>
+      <c r="M55" s="6"/>
+    </row>
+    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J56" s="6"/>
+      <c r="K56" s="6"/>
+      <c r="L56" s="6"/>
+      <c r="M56" s="6"/>
+    </row>
+    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J57" s="6"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="6"/>
+      <c r="M57" s="6"/>
+    </row>
+    <row r="58" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6"/>
+      <c r="L58" s="6"/>
+      <c r="M58" s="6"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6"/>
+      <c r="M59" s="6"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M51"/>
-  <conditionalFormatting sqref="J2:J51">
+  <autoFilter ref="A1:M59"/>
+  <conditionalFormatting sqref="J2:J59">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>"OK"</formula>
     </cfRule>
@@ -3459,7 +3867,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J51" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J59" type="list">
       <formula1>"OK,Corrección,Pendiente,No aplica"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3497,7 +3905,7 @@
         <v>10</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>324</v>
+        <v>372</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>16</v>
@@ -3520,16 +3928,16 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>325</v>
+        <v>373</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>326</v>
+        <v>374</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>327</v>
+        <v>375</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>328</v>
+        <v>376</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
@@ -3538,16 +3946,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>329</v>
+        <v>377</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>330</v>
+        <v>378</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>331</v>
+        <v>379</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>332</v>
+        <v>380</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
@@ -3556,16 +3964,16 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>333</v>
+        <v>381</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>334</v>
+        <v>382</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>335</v>
+        <v>383</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>336</v>
+        <v>384</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -3574,16 +3982,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>337</v>
+        <v>385</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>338</v>
+        <v>386</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>339</v>
+        <v>387</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>340</v>
+        <v>388</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
@@ -3592,16 +4000,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>341</v>
+        <v>389</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>342</v>
+        <v>390</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>339</v>
+        <v>387</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>343</v>
+        <v>391</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -3610,16 +4018,16 @@
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>344</v>
+        <v>392</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>345</v>
+        <v>393</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>339</v>
+        <v>387</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>346</v>
+        <v>394</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -3628,16 +4036,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>347</v>
+        <v>395</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>348</v>
+        <v>396</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>350</v>
+        <v>398</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -3676,76 +4084,76 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>351</v>
+        <v>399</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>352</v>
+        <v>400</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>353</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>354</v>
+        <v>402</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>355</v>
+        <v>403</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>356</v>
+        <v>404</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>357</v>
+        <v>405</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>358</v>
+        <v>406</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>359</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>360</v>
+        <v>408</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>361</v>
+        <v>409</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>362</v>
+        <v>410</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>363</v>
+        <v>411</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>364</v>
+        <v>412</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>365</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>366</v>
+        <v>414</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>367</v>
+        <v>415</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>368</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>369</v>
+        <v>417</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>370</v>
+        <v>418</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>42</v>
@@ -3767,7 +4175,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3782,25 +4190,25 @@
         <v>11</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>371</v>
+        <v>419</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>372</v>
+        <v>420</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>373</v>
+        <v>421</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>374</v>
+        <v>422</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>375</v>
+        <v>423</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>376</v>
+        <v>424</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>377</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3808,23 +4216,23 @@
         <v>24</v>
       </c>
       <c r="B2" s="7" t="n">
-        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$51,A2)</f>
+        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$59,A2)</f>
         <v>16</v>
       </c>
       <c r="C2" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$51,$A2,'Casos de prueba'!$J$2:$J$51,"OK")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A2,'Casos de prueba'!$J$2:$J$59,"OK")</f>
         <v>0</v>
       </c>
       <c r="D2" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$51,$A2,'Casos de prueba'!$J$2:$J$51,"Corrección")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A2,'Casos de prueba'!$J$2:$J$59,"Corrección")</f>
         <v>0</v>
       </c>
       <c r="E2" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$51,$A2,'Casos de prueba'!$J$2:$J$51,"Pendiente")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A2,'Casos de prueba'!$J$2:$J$59,"Pendiente")</f>
         <v>0</v>
       </c>
       <c r="F2" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$51,$A2,'Casos de prueba'!$J$2:$J$51,"No aplica")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A2,'Casos de prueba'!$J$2:$J$59,"No aplica")</f>
         <v>0</v>
       </c>
       <c r="G2" s="7" t="n">
@@ -3841,23 +4249,23 @@
         <v>134</v>
       </c>
       <c r="B3" s="7" t="n">
-        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$51,A3)</f>
+        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$59,A3)</f>
         <v>6</v>
       </c>
       <c r="C3" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$51,$A3,'Casos de prueba'!$J$2:$J$51,"OK")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A3,'Casos de prueba'!$J$2:$J$59,"OK")</f>
         <v>0</v>
       </c>
       <c r="D3" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$51,$A3,'Casos de prueba'!$J$2:$J$51,"Corrección")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A3,'Casos de prueba'!$J$2:$J$59,"Corrección")</f>
         <v>0</v>
       </c>
       <c r="E3" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$51,$A3,'Casos de prueba'!$J$2:$J$51,"Pendiente")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A3,'Casos de prueba'!$J$2:$J$59,"Pendiente")</f>
         <v>0</v>
       </c>
       <c r="F3" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$51,$A3,'Casos de prueba'!$J$2:$J$51,"No aplica")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A3,'Casos de prueba'!$J$2:$J$59,"No aplica")</f>
         <v>0</v>
       </c>
       <c r="G3" s="7" t="n">
@@ -3874,23 +4282,23 @@
         <v>179</v>
       </c>
       <c r="B4" s="7" t="n">
-        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$51,A4)</f>
+        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$59,A4)</f>
         <v>28</v>
       </c>
       <c r="C4" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$51,$A4,'Casos de prueba'!$J$2:$J$51,"OK")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A4,'Casos de prueba'!$J$2:$J$59,"OK")</f>
         <v>0</v>
       </c>
       <c r="D4" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$51,$A4,'Casos de prueba'!$J$2:$J$51,"Corrección")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A4,'Casos de prueba'!$J$2:$J$59,"Corrección")</f>
         <v>0</v>
       </c>
       <c r="E4" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$51,$A4,'Casos de prueba'!$J$2:$J$51,"Pendiente")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A4,'Casos de prueba'!$J$2:$J$59,"Pendiente")</f>
         <v>0</v>
       </c>
       <c r="F4" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$51,$A4,'Casos de prueba'!$J$2:$J$51,"No aplica")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A4,'Casos de prueba'!$J$2:$J$59,"No aplica")</f>
         <v>0</v>
       </c>
       <c r="G4" s="7" t="n">
@@ -3903,56 +4311,74 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="B5" s="9" t="n">
-        <f aca="false">SUM(B2:B4)</f>
-        <v>50</v>
-      </c>
-      <c r="C5" s="9" t="n">
-        <f aca="false">SUM(C2:C4)</f>
+      <c r="A5" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="B5" s="7" t="n">
+        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$59,A5)</f>
+        <v>8</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A5,'Casos de prueba'!$J$2:$J$59,"OK")</f>
         <v>0</v>
       </c>
-      <c r="D5" s="9" t="n">
-        <f aca="false">SUM(D2:D4)</f>
+      <c r="D5" s="7" t="n">
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A5,'Casos de prueba'!$J$2:$J$59,"Corrección")</f>
         <v>0</v>
       </c>
-      <c r="E5" s="9" t="n">
-        <f aca="false">SUM(E2:E4)</f>
+      <c r="E5" s="7" t="n">
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A5,'Casos de prueba'!$J$2:$J$59,"Pendiente")</f>
         <v>0</v>
       </c>
-      <c r="F5" s="9" t="n">
-        <f aca="false">SUM(F2:F4)</f>
+      <c r="F5" s="7" t="n">
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A5,'Casos de prueba'!$J$2:$J$59,"No aplica")</f>
         <v>0</v>
       </c>
-      <c r="G5" s="9" t="n">
-        <f aca="false">SUM(G2:G4)</f>
-        <v>50</v>
-      </c>
-      <c r="H5" s="10" t="n">
+      <c r="G5" s="7" t="n">
+        <f aca="false">B5-SUM(C5:F5)</f>
+        <v>8</v>
+      </c>
+      <c r="H5" s="8" t="n">
         <f aca="false">IF(B5=0,0,C5/B5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
+      <c r="A6" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="B6" s="9" t="n">
+        <f aca="false">SUM(B2:B5)</f>
+        <v>58</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <f aca="false">SUM(C2:C5)</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <f aca="false">SUM(D2:D5)</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <f aca="false">SUM(E2:E5)</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <f aca="false">SUM(F2:F5)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <f aca="false">SUM(G2:G5)</f>
+        <v>58</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <f aca="false">IF(B6=0,0,C6/B6)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="B7" s="7" t="n">
-        <f aca="false">COUNTA('Regresión acumulada'!$A$2:$A$8)</f>
-        <v>7</v>
-      </c>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
@@ -3962,11 +4388,11 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>380</v>
+        <v>427</v>
       </c>
       <c r="B8" s="7" t="n">
-        <f aca="false">COUNTIF('Regresión acumulada'!$E$2:$E$8,"OK")</f>
-        <v>0</v>
+        <f aca="false">COUNTA('Regresión acumulada'!$A$2:$A$8)</f>
+        <v>7</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -3974,6 +4400,21 @@
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="B9" s="7" t="n">
+        <f aca="false">COUNTIF('Regresión acumulada'!$E$2:$E$8,"OK")</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/documentos/2026-10-20 RQM Complemento de Modúlo de consulta de logs/T29 - Casos de prueba.xlsx
+++ b/documentos/2026-10-20 RQM Complemento de Modúlo de consulta de logs/T29 - Casos de prueba.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Resumen" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Casos de prueba'!$A$1:$M$59</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Casos de prueba'!$A$1:$M$61</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="439">
   <si>
     <t xml:space="preserve">RQM Complemento módulo de Consulta de Logs + Marca de Oferta – T29 Casos de prueba</t>
   </si>
@@ -1052,10 +1052,10 @@
     <t xml:space="preserve">Código sin artículos ni generados (ej. ZZ)</t>
   </si>
   <si>
-    <t xml:space="preserve">Generar 3.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genera ZZ-001, ZZ-002, ZZ-003.</t>
+    <t xml:space="preserve">Cantidad 3, Generar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genera ZZ-001, ZZ-002, ZZ-003 (Generado ahora = Sí).</t>
   </si>
   <si>
     <t xml:space="preserve">SELECT * FROM INTERNAL_REFERENCE_CONSECUTIVES WHERE CODE = 'ZZ';</t>
@@ -1067,10 +1067,10 @@
     <t xml:space="preserve">Consecutivos - código con artículos</t>
   </si>
   <si>
-    <t xml:space="preserve">Código con artículos (ej. el mayor es MU-025)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generar 2.</t>
+    <t xml:space="preserve">Código con artículos (ej. el mayor es MU-025), sin disponibles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cantidad 2, Generar.</t>
   </si>
   <si>
     <t xml:space="preserve">Genera MU-026 y MU-027 (por encima del mayor usado).</t>
@@ -1082,21 +1082,51 @@
     <t xml:space="preserve">E4-05</t>
   </si>
   <si>
-    <t xml:space="preserve">Consecutivos - Consultar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generados del caso anterior</t>
+    <t xml:space="preserve">Consecutivos - usado se elimina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MU-026 y MU-027 disponibles</t>
   </si>
   <si>
     <t xml:space="preserve">Crear un artículo con MU-026; Consultar MU.</t>
   </si>
   <si>
-    <t xml:space="preserve">Solo aparece MU-027.</t>
+    <t xml:space="preserve">Solo aparece MU-027 y MU-026 ya no está en la tabla.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECT * FROM INTERNAL_REFERENCE_CONSECUTIVES WHERE CODE = 'MU'; -- solo 27</t>
   </si>
   <si>
     <t xml:space="preserve">E4-06</t>
   </si>
   <si>
+    <t xml:space="preserve">Consecutivos - completar hasta N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MU-027 disponible; mayor usado MU-026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cantidad 4, Generar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crea MU-028 a MU-030; quedan 4 disponibles (027 con Generado ahora = No).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E4-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consecutivos - ya hay suficientes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 disponibles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No genera; mensaje informativo; muestra los 4 disponibles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E4-08</t>
+  </si>
+  <si>
     <t xml:space="preserve">Consecutivos - minúsculas y prefijos</t>
   </si>
   <si>
@@ -1106,7 +1136,7 @@
     <t xml:space="preserve">'mu' = MU; MUX no se mezcla con MU.</t>
   </si>
   <si>
-    <t xml:space="preserve">E4-07</t>
+    <t xml:space="preserve">E4-09</t>
   </si>
   <si>
     <t xml:space="preserve">C6</t>
@@ -1127,7 +1157,7 @@
     <t xml:space="preserve">SELECT CODE, CONSECUTIVE, COUNT(*) FROM INTERNAL_REFERENCE_CONSECUTIVES GROUP BY CODE, CONSECUTIVE HAVING COUNT(*) &gt; 1; -- 0 filas</t>
   </si>
   <si>
-    <t xml:space="preserve">E4-08</t>
+    <t xml:space="preserve">E4-10</t>
   </si>
   <si>
     <t xml:space="preserve">C4</t>
@@ -1884,7 +1914,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -3724,7 +3754,7 @@
       <c r="L55" s="6"/>
       <c r="M55" s="6"/>
     </row>
-    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
         <v>350</v>
       </c>
@@ -3750,7 +3780,7 @@
         <v>354</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>42</v>
+        <v>355</v>
       </c>
       <c r="J56" s="6"/>
       <c r="K56" s="6"/>
@@ -3759,7 +3789,7 @@
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>325</v>
@@ -3768,19 +3798,19 @@
         <v>338</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E57" s="5" t="s">
         <v>334</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>42</v>
+        <v>358</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="I57" s="5" t="s">
         <v>42</v>
@@ -3790,63 +3820,63 @@
       <c r="L57" s="6"/>
       <c r="M57" s="6"/>
     </row>
-    <row r="58" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>325</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>362</v>
+        <v>334</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>42</v>
+        <v>363</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>363</v>
+        <v>341</v>
       </c>
       <c r="H58" s="5" t="s">
         <v>364</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>365</v>
+        <v>42</v>
       </c>
       <c r="J58" s="6"/>
       <c r="K58" s="6"/>
       <c r="L58" s="6"/>
       <c r="M58" s="6"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>325</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>367</v>
+        <v>338</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>369</v>
+        <v>334</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>42</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="I59" s="5" t="s">
         <v>42</v>
@@ -3856,9 +3886,75 @@
       <c r="L59" s="6"/>
       <c r="M59" s="6"/>
     </row>
+    <row r="60" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="6"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="6"/>
+      <c r="M61" s="6"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M59"/>
-  <conditionalFormatting sqref="J2:J59">
+  <autoFilter ref="A1:M61"/>
+  <conditionalFormatting sqref="J2:J61">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>"OK"</formula>
     </cfRule>
@@ -3867,7 +3963,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J59" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J61" type="list">
       <formula1>"OK,Corrección,Pendiente,No aplica"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3905,7 +4001,7 @@
         <v>10</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>16</v>
@@ -3928,16 +4024,16 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
@@ -3946,16 +4042,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
@@ -3964,16 +4060,16 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -3982,16 +4078,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
@@ -4000,16 +4096,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -4018,16 +4114,16 @@
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -4036,16 +4132,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -4084,76 +4180,76 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>42</v>
@@ -4190,25 +4286,25 @@
         <v>11</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4216,23 +4312,23 @@
         <v>24</v>
       </c>
       <c r="B2" s="7" t="n">
-        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$59,A2)</f>
+        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$61,A2)</f>
         <v>16</v>
       </c>
       <c r="C2" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A2,'Casos de prueba'!$J$2:$J$59,"OK")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A2,'Casos de prueba'!$J$2:$J$61,"OK")</f>
         <v>0</v>
       </c>
       <c r="D2" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A2,'Casos de prueba'!$J$2:$J$59,"Corrección")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A2,'Casos de prueba'!$J$2:$J$61,"Corrección")</f>
         <v>0</v>
       </c>
       <c r="E2" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A2,'Casos de prueba'!$J$2:$J$59,"Pendiente")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A2,'Casos de prueba'!$J$2:$J$61,"Pendiente")</f>
         <v>0</v>
       </c>
       <c r="F2" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A2,'Casos de prueba'!$J$2:$J$59,"No aplica")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A2,'Casos de prueba'!$J$2:$J$61,"No aplica")</f>
         <v>0</v>
       </c>
       <c r="G2" s="7" t="n">
@@ -4249,23 +4345,23 @@
         <v>134</v>
       </c>
       <c r="B3" s="7" t="n">
-        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$59,A3)</f>
+        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$61,A3)</f>
         <v>6</v>
       </c>
       <c r="C3" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A3,'Casos de prueba'!$J$2:$J$59,"OK")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A3,'Casos de prueba'!$J$2:$J$61,"OK")</f>
         <v>0</v>
       </c>
       <c r="D3" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A3,'Casos de prueba'!$J$2:$J$59,"Corrección")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A3,'Casos de prueba'!$J$2:$J$61,"Corrección")</f>
         <v>0</v>
       </c>
       <c r="E3" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A3,'Casos de prueba'!$J$2:$J$59,"Pendiente")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A3,'Casos de prueba'!$J$2:$J$61,"Pendiente")</f>
         <v>0</v>
       </c>
       <c r="F3" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A3,'Casos de prueba'!$J$2:$J$59,"No aplica")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A3,'Casos de prueba'!$J$2:$J$61,"No aplica")</f>
         <v>0</v>
       </c>
       <c r="G3" s="7" t="n">
@@ -4282,23 +4378,23 @@
         <v>179</v>
       </c>
       <c r="B4" s="7" t="n">
-        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$59,A4)</f>
+        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$61,A4)</f>
         <v>28</v>
       </c>
       <c r="C4" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A4,'Casos de prueba'!$J$2:$J$59,"OK")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A4,'Casos de prueba'!$J$2:$J$61,"OK")</f>
         <v>0</v>
       </c>
       <c r="D4" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A4,'Casos de prueba'!$J$2:$J$59,"Corrección")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A4,'Casos de prueba'!$J$2:$J$61,"Corrección")</f>
         <v>0</v>
       </c>
       <c r="E4" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A4,'Casos de prueba'!$J$2:$J$59,"Pendiente")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A4,'Casos de prueba'!$J$2:$J$61,"Pendiente")</f>
         <v>0</v>
       </c>
       <c r="F4" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A4,'Casos de prueba'!$J$2:$J$59,"No aplica")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A4,'Casos de prueba'!$J$2:$J$61,"No aplica")</f>
         <v>0</v>
       </c>
       <c r="G4" s="7" t="n">
@@ -4315,28 +4411,28 @@
         <v>325</v>
       </c>
       <c r="B5" s="7" t="n">
-        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$59,A5)</f>
-        <v>8</v>
+        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$61,A5)</f>
+        <v>10</v>
       </c>
       <c r="C5" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A5,'Casos de prueba'!$J$2:$J$59,"OK")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A5,'Casos de prueba'!$J$2:$J$61,"OK")</f>
         <v>0</v>
       </c>
       <c r="D5" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A5,'Casos de prueba'!$J$2:$J$59,"Corrección")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A5,'Casos de prueba'!$J$2:$J$61,"Corrección")</f>
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A5,'Casos de prueba'!$J$2:$J$59,"Pendiente")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A5,'Casos de prueba'!$J$2:$J$61,"Pendiente")</f>
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$59,$A5,'Casos de prueba'!$J$2:$J$59,"No aplica")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A5,'Casos de prueba'!$J$2:$J$61,"No aplica")</f>
         <v>0</v>
       </c>
       <c r="G5" s="7" t="n">
         <f aca="false">B5-SUM(C5:F5)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H5" s="8" t="n">
         <f aca="false">IF(B5=0,0,C5/B5)</f>
@@ -4345,11 +4441,11 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">SUM(B2:B5)</f>
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C6" s="9" t="n">
         <f aca="false">SUM(C2:C5)</f>
@@ -4369,7 +4465,7 @@
       </c>
       <c r="G6" s="9" t="n">
         <f aca="false">SUM(G2:G5)</f>
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H6" s="10" t="n">
         <f aca="false">IF(B6=0,0,C6/B6)</f>
@@ -4388,7 +4484,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">COUNTA('Regresión acumulada'!$A$2:$A$8)</f>
@@ -4403,7 +4499,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="B9" s="7" t="n">
         <f aca="false">COUNTIF('Regresión acumulada'!$E$2:$E$8,"OK")</f>

--- a/documentos/2026-10-20 RQM Complemento de Modúlo de consulta de logs/T29 - Casos de prueba.xlsx
+++ b/documentos/2026-10-20 RQM Complemento de Modúlo de consulta de logs/T29 - Casos de prueba.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Resumen" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Casos de prueba'!$A$1:$M$61</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Casos de prueba'!$A$1:$M$63</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="450">
   <si>
     <t xml:space="preserve">RQM Complemento módulo de Consulta de Logs + Marca de Oferta – T29 Casos de prueba</t>
   </si>
@@ -1139,6 +1139,39 @@
     <t xml:space="preserve">E4-09</t>
   </si>
   <si>
+    <t xml:space="preserve">Consecutivos - complementos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MU-031 disponible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crear un artículo con MU-031-2 (o MU-031-X); Consultar MU.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MU-031 se elimina de los disponibles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E4-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consecutivos - referencias de 2 dígitos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Artículos existentes MU-40 o MU-40-1 (mayor del código)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cantidad 1 sin disponibles, Generar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genera MU-041 (MU-40 se toma como 040).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECT INTERNAL_REFERENCE FROM items WHERE INTERNAL_REFERENCE LIKE 'MU-%';</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E4-11</t>
+  </si>
+  <si>
     <t xml:space="preserve">C6</t>
   </si>
   <si>
@@ -1157,7 +1190,7 @@
     <t xml:space="preserve">SELECT CODE, CONSECUTIVE, COUNT(*) FROM INTERNAL_REFERENCE_CONSECUTIVES GROUP BY CODE, CONSECUTIVE HAVING COUNT(*) &gt; 1; -- 0 filas</t>
   </si>
   <si>
-    <t xml:space="preserve">E4-10</t>
+    <t xml:space="preserve">E4-12</t>
   </si>
   <si>
     <t xml:space="preserve">C4</t>
@@ -1914,7 +1947,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -3886,7 +3919,7 @@
       <c r="L59" s="6"/>
       <c r="M59" s="6"/>
     </row>
-    <row r="60" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
         <v>369</v>
       </c>
@@ -3894,67 +3927,133 @@
         <v>325</v>
       </c>
       <c r="C60" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="D60" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="D60" s="5" t="s">
+      <c r="E60" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="F60" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="E60" s="5" t="s">
+      <c r="G60" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="F60" s="5" t="s">
+      <c r="H60" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="I60" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="H60" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="I60" s="5" t="s">
-        <v>375</v>
       </c>
       <c r="J60" s="6"/>
       <c r="K60" s="6"/>
       <c r="L60" s="6"/>
       <c r="M60" s="6"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>325</v>
       </c>
       <c r="C61" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="G61" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="D61" s="5" t="s">
+      <c r="H61" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="I61" s="5" t="s">
         <v>379</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="H61" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="I61" s="5" t="s">
-        <v>42</v>
       </c>
       <c r="J61" s="6"/>
       <c r="K61" s="6"/>
       <c r="L61" s="6"/>
       <c r="M61" s="6"/>
     </row>
+    <row r="62" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="J62" s="6"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="6"/>
+      <c r="M62" s="6"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="6"/>
+      <c r="M63" s="6"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M61"/>
-  <conditionalFormatting sqref="J2:J61">
+  <autoFilter ref="A1:M63"/>
+  <conditionalFormatting sqref="J2:J63">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>"OK"</formula>
     </cfRule>
@@ -3963,7 +4062,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J61" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J63" type="list">
       <formula1>"OK,Corrección,Pendiente,No aplica"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4001,7 +4100,7 @@
         <v>10</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>16</v>
@@ -4024,16 +4123,16 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
@@ -4042,16 +4141,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
@@ -4060,16 +4159,16 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -4078,16 +4177,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
@@ -4096,16 +4195,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -4114,16 +4213,16 @@
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -4132,16 +4231,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -4180,76 +4279,76 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>42</v>
@@ -4286,25 +4385,25 @@
         <v>11</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4312,23 +4411,23 @@
         <v>24</v>
       </c>
       <c r="B2" s="7" t="n">
-        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$61,A2)</f>
+        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$63,A2)</f>
         <v>16</v>
       </c>
       <c r="C2" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A2,'Casos de prueba'!$J$2:$J$61,"OK")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A2,'Casos de prueba'!$J$2:$J$63,"OK")</f>
         <v>0</v>
       </c>
       <c r="D2" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A2,'Casos de prueba'!$J$2:$J$61,"Corrección")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A2,'Casos de prueba'!$J$2:$J$63,"Corrección")</f>
         <v>0</v>
       </c>
       <c r="E2" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A2,'Casos de prueba'!$J$2:$J$61,"Pendiente")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A2,'Casos de prueba'!$J$2:$J$63,"Pendiente")</f>
         <v>0</v>
       </c>
       <c r="F2" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A2,'Casos de prueba'!$J$2:$J$61,"No aplica")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A2,'Casos de prueba'!$J$2:$J$63,"No aplica")</f>
         <v>0</v>
       </c>
       <c r="G2" s="7" t="n">
@@ -4345,23 +4444,23 @@
         <v>134</v>
       </c>
       <c r="B3" s="7" t="n">
-        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$61,A3)</f>
+        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$63,A3)</f>
         <v>6</v>
       </c>
       <c r="C3" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A3,'Casos de prueba'!$J$2:$J$61,"OK")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A3,'Casos de prueba'!$J$2:$J$63,"OK")</f>
         <v>0</v>
       </c>
       <c r="D3" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A3,'Casos de prueba'!$J$2:$J$61,"Corrección")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A3,'Casos de prueba'!$J$2:$J$63,"Corrección")</f>
         <v>0</v>
       </c>
       <c r="E3" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A3,'Casos de prueba'!$J$2:$J$61,"Pendiente")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A3,'Casos de prueba'!$J$2:$J$63,"Pendiente")</f>
         <v>0</v>
       </c>
       <c r="F3" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A3,'Casos de prueba'!$J$2:$J$61,"No aplica")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A3,'Casos de prueba'!$J$2:$J$63,"No aplica")</f>
         <v>0</v>
       </c>
       <c r="G3" s="7" t="n">
@@ -4378,23 +4477,23 @@
         <v>179</v>
       </c>
       <c r="B4" s="7" t="n">
-        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$61,A4)</f>
+        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$63,A4)</f>
         <v>28</v>
       </c>
       <c r="C4" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A4,'Casos de prueba'!$J$2:$J$61,"OK")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A4,'Casos de prueba'!$J$2:$J$63,"OK")</f>
         <v>0</v>
       </c>
       <c r="D4" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A4,'Casos de prueba'!$J$2:$J$61,"Corrección")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A4,'Casos de prueba'!$J$2:$J$63,"Corrección")</f>
         <v>0</v>
       </c>
       <c r="E4" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A4,'Casos de prueba'!$J$2:$J$61,"Pendiente")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A4,'Casos de prueba'!$J$2:$J$63,"Pendiente")</f>
         <v>0</v>
       </c>
       <c r="F4" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A4,'Casos de prueba'!$J$2:$J$61,"No aplica")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A4,'Casos de prueba'!$J$2:$J$63,"No aplica")</f>
         <v>0</v>
       </c>
       <c r="G4" s="7" t="n">
@@ -4411,28 +4510,28 @@
         <v>325</v>
       </c>
       <c r="B5" s="7" t="n">
-        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$61,A5)</f>
-        <v>10</v>
+        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$63,A5)</f>
+        <v>12</v>
       </c>
       <c r="C5" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A5,'Casos de prueba'!$J$2:$J$61,"OK")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A5,'Casos de prueba'!$J$2:$J$63,"OK")</f>
         <v>0</v>
       </c>
       <c r="D5" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A5,'Casos de prueba'!$J$2:$J$61,"Corrección")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A5,'Casos de prueba'!$J$2:$J$63,"Corrección")</f>
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A5,'Casos de prueba'!$J$2:$J$61,"Pendiente")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A5,'Casos de prueba'!$J$2:$J$63,"Pendiente")</f>
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$61,$A5,'Casos de prueba'!$J$2:$J$61,"No aplica")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A5,'Casos de prueba'!$J$2:$J$63,"No aplica")</f>
         <v>0</v>
       </c>
       <c r="G5" s="7" t="n">
         <f aca="false">B5-SUM(C5:F5)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H5" s="8" t="n">
         <f aca="false">IF(B5=0,0,C5/B5)</f>
@@ -4441,11 +4540,11 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">SUM(B2:B5)</f>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C6" s="9" t="n">
         <f aca="false">SUM(C2:C5)</f>
@@ -4465,7 +4564,7 @@
       </c>
       <c r="G6" s="9" t="n">
         <f aca="false">SUM(G2:G5)</f>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H6" s="10" t="n">
         <f aca="false">IF(B6=0,0,C6/B6)</f>
@@ -4484,7 +4583,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">COUNTA('Regresión acumulada'!$A$2:$A$8)</f>
@@ -4499,7 +4598,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="B9" s="7" t="n">
         <f aca="false">COUNTIF('Regresión acumulada'!$E$2:$E$8,"OK")</f>

--- a/documentos/2026-10-20 RQM Complemento de Modúlo de consulta de logs/T29 - Casos de prueba.xlsx
+++ b/documentos/2026-10-20 RQM Complemento de Modúlo de consulta de logs/T29 - Casos de prueba.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Resumen" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Casos de prueba'!$A$1:$M$63</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Casos de prueba'!$A$1:$M$65</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="460">
   <si>
     <t xml:space="preserve">RQM Complemento módulo de Consulta de Logs + Marca de Oferta – T29 Casos de prueba</t>
   </si>
@@ -1172,6 +1172,36 @@
     <t xml:space="preserve">E4-11</t>
   </si>
   <si>
+    <t xml:space="preserve">Consecutivos - 1 dígito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Único artículo del código: ZY-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cantidad 1, Generar ZY.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genera ZY-006 (ZY-5 = 005).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E4-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consecutivos - referencias que no cumplen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Único artículo del código: ZX-25X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consultar y Generar 1 para ZX.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genera ZX-001; la lista de referencias que no se toman como consecutivo muestra ZX-25X con su motivo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E4-13</t>
+  </si>
+  <si>
     <t xml:space="preserve">C6</t>
   </si>
   <si>
@@ -1190,7 +1220,7 @@
     <t xml:space="preserve">SELECT CODE, CONSECUTIVE, COUNT(*) FROM INTERNAL_REFERENCE_CONSECUTIVES GROUP BY CODE, CONSECUTIVE HAVING COUNT(*) &gt; 1; -- 0 filas</t>
   </si>
   <si>
-    <t xml:space="preserve">E4-12</t>
+    <t xml:space="preserve">E4-14</t>
   </si>
   <si>
     <t xml:space="preserve">C4</t>
@@ -1947,7 +1977,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -3985,7 +4015,7 @@
       <c r="L61" s="6"/>
       <c r="M61" s="6"/>
     </row>
-    <row r="62" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
         <v>380</v>
       </c>
@@ -3993,55 +4023,55 @@
         <v>325</v>
       </c>
       <c r="C62" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="D62" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="E62" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="F62" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="E62" s="5" t="s">
+      <c r="G62" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="F62" s="5" t="s">
+      <c r="H62" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="I62" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="H62" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="I62" s="5" t="s">
-        <v>386</v>
       </c>
       <c r="J62" s="6"/>
       <c r="K62" s="6"/>
       <c r="L62" s="6"/>
       <c r="M62" s="6"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>325</v>
       </c>
       <c r="C63" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="G63" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="H63" s="5" t="s">
         <v>389</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="H63" s="5" t="s">
-        <v>392</v>
       </c>
       <c r="I63" s="5" t="s">
         <v>42</v>
@@ -4051,9 +4081,75 @@
       <c r="L63" s="6"/>
       <c r="M63" s="6"/>
     </row>
+    <row r="64" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="H64" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="J64" s="6"/>
+      <c r="K64" s="6"/>
+      <c r="L64" s="6"/>
+      <c r="M64" s="6"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J65" s="6"/>
+      <c r="K65" s="6"/>
+      <c r="L65" s="6"/>
+      <c r="M65" s="6"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M63"/>
-  <conditionalFormatting sqref="J2:J63">
+  <autoFilter ref="A1:M65"/>
+  <conditionalFormatting sqref="J2:J65">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>"OK"</formula>
     </cfRule>
@@ -4062,7 +4158,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J63" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J65" type="list">
       <formula1>"OK,Corrección,Pendiente,No aplica"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4100,7 +4196,7 @@
         <v>10</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>16</v>
@@ -4123,16 +4219,16 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
@@ -4141,16 +4237,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
@@ -4159,16 +4255,16 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -4177,16 +4273,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
@@ -4195,16 +4291,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -4213,16 +4309,16 @@
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -4231,16 +4327,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -4279,76 +4375,76 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>42</v>
@@ -4385,25 +4481,25 @@
         <v>11</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4411,23 +4507,23 @@
         <v>24</v>
       </c>
       <c r="B2" s="7" t="n">
-        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$63,A2)</f>
+        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$65,A2)</f>
         <v>16</v>
       </c>
       <c r="C2" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A2,'Casos de prueba'!$J$2:$J$63,"OK")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$65,$A2,'Casos de prueba'!$J$2:$J$65,"OK")</f>
         <v>0</v>
       </c>
       <c r="D2" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A2,'Casos de prueba'!$J$2:$J$63,"Corrección")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$65,$A2,'Casos de prueba'!$J$2:$J$65,"Corrección")</f>
         <v>0</v>
       </c>
       <c r="E2" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A2,'Casos de prueba'!$J$2:$J$63,"Pendiente")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$65,$A2,'Casos de prueba'!$J$2:$J$65,"Pendiente")</f>
         <v>0</v>
       </c>
       <c r="F2" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A2,'Casos de prueba'!$J$2:$J$63,"No aplica")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$65,$A2,'Casos de prueba'!$J$2:$J$65,"No aplica")</f>
         <v>0</v>
       </c>
       <c r="G2" s="7" t="n">
@@ -4444,23 +4540,23 @@
         <v>134</v>
       </c>
       <c r="B3" s="7" t="n">
-        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$63,A3)</f>
+        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$65,A3)</f>
         <v>6</v>
       </c>
       <c r="C3" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A3,'Casos de prueba'!$J$2:$J$63,"OK")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$65,$A3,'Casos de prueba'!$J$2:$J$65,"OK")</f>
         <v>0</v>
       </c>
       <c r="D3" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A3,'Casos de prueba'!$J$2:$J$63,"Corrección")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$65,$A3,'Casos de prueba'!$J$2:$J$65,"Corrección")</f>
         <v>0</v>
       </c>
       <c r="E3" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A3,'Casos de prueba'!$J$2:$J$63,"Pendiente")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$65,$A3,'Casos de prueba'!$J$2:$J$65,"Pendiente")</f>
         <v>0</v>
       </c>
       <c r="F3" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A3,'Casos de prueba'!$J$2:$J$63,"No aplica")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$65,$A3,'Casos de prueba'!$J$2:$J$65,"No aplica")</f>
         <v>0</v>
       </c>
       <c r="G3" s="7" t="n">
@@ -4477,23 +4573,23 @@
         <v>179</v>
       </c>
       <c r="B4" s="7" t="n">
-        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$63,A4)</f>
+        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$65,A4)</f>
         <v>28</v>
       </c>
       <c r="C4" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A4,'Casos de prueba'!$J$2:$J$63,"OK")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$65,$A4,'Casos de prueba'!$J$2:$J$65,"OK")</f>
         <v>0</v>
       </c>
       <c r="D4" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A4,'Casos de prueba'!$J$2:$J$63,"Corrección")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$65,$A4,'Casos de prueba'!$J$2:$J$65,"Corrección")</f>
         <v>0</v>
       </c>
       <c r="E4" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A4,'Casos de prueba'!$J$2:$J$63,"Pendiente")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$65,$A4,'Casos de prueba'!$J$2:$J$65,"Pendiente")</f>
         <v>0</v>
       </c>
       <c r="F4" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A4,'Casos de prueba'!$J$2:$J$63,"No aplica")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$65,$A4,'Casos de prueba'!$J$2:$J$65,"No aplica")</f>
         <v>0</v>
       </c>
       <c r="G4" s="7" t="n">
@@ -4510,28 +4606,28 @@
         <v>325</v>
       </c>
       <c r="B5" s="7" t="n">
-        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$63,A5)</f>
-        <v>12</v>
+        <f aca="false">COUNTIF('Casos de prueba'!$B$2:$B$65,A5)</f>
+        <v>14</v>
       </c>
       <c r="C5" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A5,'Casos de prueba'!$J$2:$J$63,"OK")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$65,$A5,'Casos de prueba'!$J$2:$J$65,"OK")</f>
         <v>0</v>
       </c>
       <c r="D5" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A5,'Casos de prueba'!$J$2:$J$63,"Corrección")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$65,$A5,'Casos de prueba'!$J$2:$J$65,"Corrección")</f>
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A5,'Casos de prueba'!$J$2:$J$63,"Pendiente")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$65,$A5,'Casos de prueba'!$J$2:$J$65,"Pendiente")</f>
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$63,$A5,'Casos de prueba'!$J$2:$J$63,"No aplica")</f>
+        <f aca="false">COUNTIFS('Casos de prueba'!$B$2:$B$65,$A5,'Casos de prueba'!$J$2:$J$65,"No aplica")</f>
         <v>0</v>
       </c>
       <c r="G5" s="7" t="n">
         <f aca="false">B5-SUM(C5:F5)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H5" s="8" t="n">
         <f aca="false">IF(B5=0,0,C5/B5)</f>
@@ -4540,11 +4636,11 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">SUM(B2:B5)</f>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C6" s="9" t="n">
         <f aca="false">SUM(C2:C5)</f>
@@ -4564,7 +4660,7 @@
       </c>
       <c r="G6" s="9" t="n">
         <f aca="false">SUM(G2:G5)</f>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H6" s="10" t="n">
         <f aca="false">IF(B6=0,0,C6/B6)</f>
@@ -4583,7 +4679,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">COUNTA('Regresión acumulada'!$A$2:$A$8)</f>
@@ -4598,7 +4694,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="B9" s="7" t="n">
         <f aca="false">COUNTIF('Regresión acumulada'!$E$2:$E$8,"OK")</f>

--- a/documentos/2026-10-20 RQM Complemento de Modúlo de consulta de logs/T29 - Casos de prueba.xlsx
+++ b/documentos/2026-10-20 RQM Complemento de Modúlo de consulta de logs/T29 - Casos de prueba.xlsx
@@ -607,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" style="11" min="1" max="1"/>
@@ -2521,17 +2521,17 @@
       </c>
       <c r="J36" s="18" t="inlineStr">
         <is>
-          <t>Corrección</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K36" s="18" t="inlineStr">
         <is>
-          <t>Bloqueado por script 18: falla con 'Incorrect syntax near +' (EXEC #RQM_T26_APPLY recibe expresiones con + CHAR(13)... como argumentos; T-SQL no lo permite). No alteró ningún SP (solo insertó los 8 respaldos). La app falla al abrir el reporte: SqlException 8145 '@IsSpecialOrder is not a parameter for procedure SP_GET_CUSTOMER_ORDER_REPORT'.</t>
+          <t>Script 18 corregido (EXEC no admite expresiones; textos en variables). Ejecutado 2 veces sobre la BD de pruebas restaurada (SP reales): 8 "actualizado", sin errores. Reversa probada en BD de ensayo. Falta E3-14 a E3-23 en la aplicación.</t>
         </is>
       </c>
       <c r="L36" s="18" t="inlineStr">
         <is>
-          <t>Claude App</t>
+          <t>Claude (nube)</t>
         </is>
       </c>
       <c r="M36" s="18" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>Sin errores; objetos creados una vez.</t>
+          <t>Sin errores; objetos creados una vez. Sobre la versión anterior: "CODE ajustado a varchar(5)".</t>
         </is>
       </c>
       <c r="I52" s="17" t="inlineStr">
@@ -3598,12 +3598,12 @@
       </c>
       <c r="K52" s="18" t="inlineStr">
         <is>
-          <t>Script 20 ejecutado; objetos creados (2 tablas, 2 funciones, 4 SP).</t>
+          <t>Nueva versión del 20: 1ª ejecución sobre la anterior ajustó CODE a varchar(5) conservando los consecutivos de prueba; 2ª sin cambios. Reversa + base limpia + 2 ejecuciones: OK.</t>
         </is>
       </c>
       <c r="L52" s="18" t="inlineStr">
         <is>
-          <t>Claude App</t>
+          <t>Claude (nube)</t>
         </is>
       </c>
       <c r="M52" s="18" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="G53" s="17" t="inlineStr">
         <is>
-          <t>Generar sin código; con espacios; con 7 caracteres; cantidad 0.</t>
+          <t>Consultar y Generar sin código; código de 7 caracteres; con guion; con _; cantidad 0 y 1001; corregir y dar un clic en Generar.</t>
         </is>
       </c>
       <c r="H53" s="17" t="inlineStr">
         <is>
-          <t>Mensajes de validación; no genera.</t>
+          <t>Mensaje de validación debajo de los campos, sin cortar el código ni cambiar la cantidad; al corregir se retira el mensaje y el primer clic abre la confirmación.</t>
         </is>
       </c>
       <c r="I53" s="17" t="inlineStr">
@@ -3660,17 +3660,17 @@
       </c>
       <c r="J53" s="18" t="inlineStr">
         <is>
-          <t>Corrección</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K53" s="18" t="inlineStr">
         <is>
-          <t>Sin código: 'El código es obligatorio.' OK. Con espacios: 'El código no puede contener espacios.' OK. 7 caracteres: el campo corta a 6 (ABCDEF) y pide confirmación para generar ABCDEF (no hay mensaje). Cantidad 0: el campo vuelve a 1 sin mensaje. Además: tras un error, el primer clic en Generar no hace nada y el mensaje anterior queda visible aunque se corrija el código.</t>
+          <t>Corregido: sin MaxLength ni Min en los campos; validación con mensaje; mensaje debajo de los campos y se retira al cambiar código o cantidad. Pantalla P02–P11 OK.</t>
         </is>
       </c>
       <c r="L53" s="18" t="inlineStr">
         <is>
-          <t>Claude App</t>
+          <t>Claude (nube)</t>
         </is>
       </c>
       <c r="M53" s="18" t="inlineStr">
@@ -3799,12 +3799,12 @@
       </c>
       <c r="K55" s="18" t="inlineStr">
         <is>
-          <t>MU (mayor usado MU-451): genera MU-452 y MU-453 (vía SP).</t>
+          <t>MU (mayor usado MU-451): genera MU-452 y MU-453 (vía SP). Re-validado con la regla nueva.</t>
         </is>
       </c>
       <c r="L55" s="18" t="inlineStr">
         <is>
-          <t>Claude App</t>
+          <t>Claude (nube)</t>
         </is>
       </c>
       <c r="M55" s="18" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="H61" s="17" t="inlineStr">
         <is>
-          <t>Genera MU-041 (MU-40 se toma como 040).</t>
+          <t>Genera MU-041 (MU-40 = 40; cualquier complemento después del número).</t>
         </is>
       </c>
       <c r="I61" s="17" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="L61" s="18" t="inlineStr">
         <is>
-          <t>Claude App</t>
+          <t>Claude (nube)</t>
         </is>
       </c>
       <c r="M61" s="18" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="F63" s="17" t="inlineStr">
         <is>
-          <t>Único artículo del código: ZX-25X</t>
+          <t>Único artículo del código: ZX-25X (complemento pegado)</t>
         </is>
       </c>
       <c r="G63" s="17" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="H63" s="17" t="inlineStr">
         <is>
-          <t>Genera ZX-001; la lista de referencias que no se toman como consecutivo muestra ZX-25X con su motivo.</t>
+          <t>Regla nueva: ZX-25X cuenta como 25 y el siguiente es ZX-026. Las referencias sin número después del guion (TH-XXXL) aparecen como no conformes con su motivo.</t>
         </is>
       </c>
       <c r="I63" s="17" t="inlineStr">
@@ -4335,12 +4335,12 @@
       </c>
       <c r="K63" s="18" t="inlineStr">
         <is>
-          <t>ZX-25X: genera ZX-001; no conforme con motivo 'Los dígitos están seguidos de "X"...'.</t>
+          <t>Regla aprobada el 24/10: complemento pegado cuenta (CP-59T = 59, ZX-25X = 25). TH: 26 no conformes con motivo "Después del guion no hay un número".</t>
         </is>
       </c>
       <c r="L63" s="18" t="inlineStr">
         <is>
-          <t>Claude App</t>
+          <t>Claude (nube)</t>
         </is>
       </c>
       <c r="M63" s="18" t="inlineStr">
@@ -4397,17 +4397,17 @@
       </c>
       <c r="J64" s="18" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K64" s="18" t="inlineStr">
         <is>
-          <t>No se ejecutaron dos sesiones simultáneas. Consulta de duplicados = 0 filas (PK código+consecutivo).</t>
+          <t>3 sesiones simultáneas × 150 generaciones + consultas del mismo código: 0 errores, 0 duplicados, sin bloqueos mutuos; quedaron exactamente 150.</t>
         </is>
       </c>
       <c r="L64" s="18" t="inlineStr">
         <is>
-          <t>Claude App</t>
+          <t>Claude (nube)</t>
         </is>
       </c>
       <c r="M64" s="18" t="inlineStr">
@@ -4464,20 +4464,690 @@
       </c>
       <c r="J65" s="18" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K65" s="18" t="inlineStr">
         <is>
-          <t>No hay SDK .NET en este equipo: Andrés debe ejecutar dotnet test.</t>
+          <t>dotnet test: 44/44 OK (reglas nuevas: 5 caracteres, Ñ, espacio interno, signos, formato 3/4 dígitos, cantidad 1–1000).</t>
         </is>
       </c>
       <c r="L65" s="18" t="inlineStr">
         <is>
-          <t>Claude App</t>
+          <t>Claude (nube)</t>
         </is>
       </c>
       <c r="M65" s="18" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1" s="12">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>E4-15</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D66" s="17" t="inlineStr">
+        <is>
+          <t>Consecutivos - 4 dígitos (VA)</t>
+        </is>
+      </c>
+      <c r="E66" s="17" t="inlineStr">
+        <is>
+          <t>Modificación de artículos</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="inlineStr">
+        <is>
+          <t>Mayor usado VA-1226 (incluye VA-1015-1 y VA-984SURA)</t>
+        </is>
+      </c>
+      <c r="G66" s="17" t="inlineStr">
+        <is>
+          <t>Generar 3 para VA.</t>
+        </is>
+      </c>
+      <c r="H66" s="17" t="inlineStr">
+        <is>
+          <t>VA-1227, VA-1228, VA-1229; VA sin no conformes.</t>
+        </is>
+      </c>
+      <c r="I66" s="17" t="inlineStr">
+        <is>
+          <t>SELECT MAX(CONSECUTIVE) FROM dbo.FN_INTERNAL_REFERENCE_USED_CONSECUTIVES('VA'); -- 1226</t>
+        </is>
+      </c>
+      <c r="J66" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K66" s="18" t="inlineStr">
+        <is>
+          <t>Pantalla P13/P14 OK.</t>
+        </is>
+      </c>
+      <c r="L66" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M66" s="18" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1" s="12">
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t>E4-16</t>
+        </is>
+      </c>
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="C67" s="17" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D67" s="17" t="inlineStr">
+        <is>
+          <t>Consecutivos - código con espacio</t>
+        </is>
+      </c>
+      <c r="E67" s="17" t="inlineStr">
+        <is>
+          <t>Modificación de artículos</t>
+        </is>
+      </c>
+      <c r="F67" s="17" t="inlineStr">
+        <is>
+          <t>Mayor usado PM VA-825</t>
+        </is>
+      </c>
+      <c r="G67" s="17" t="inlineStr">
+        <is>
+          <t>Generar 2 para "pm va".</t>
+        </is>
+      </c>
+      <c r="H67" s="17" t="inlineStr">
+        <is>
+          <t>PM VA-826 y PM VA-827.</t>
+        </is>
+      </c>
+      <c r="I67" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J67" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K67" s="18" t="inlineStr">
+        <is>
+          <t>Pantalla P15 OK.</t>
+        </is>
+      </c>
+      <c r="L67" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M67" s="18" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="15" customHeight="1" s="12">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t>E4-17</t>
+        </is>
+      </c>
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="C68" s="17" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D68" s="17" t="inlineStr">
+        <is>
+          <t>Consecutivos - complementos</t>
+        </is>
+      </c>
+      <c r="E68" s="17" t="inlineStr">
+        <is>
+          <t>Modificación de artículos</t>
+        </is>
+      </c>
+      <c r="F68" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="17" t="inlineStr">
+        <is>
+          <t>Referencias con complemento con guion (VA-1015-1), pegado (CP-59T, VA-984SURA) y con espacio (MU-1 ROJO).</t>
+        </is>
+      </c>
+      <c r="H68" s="17" t="inlineStr">
+        <is>
+          <t>Todas cuentan: 1015, 59, 984, 1.</t>
+        </is>
+      </c>
+      <c r="I68" s="17" t="inlineStr">
+        <is>
+          <t>P07 casos R07–R10, R15</t>
+        </is>
+      </c>
+      <c r="J68" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K68" s="18" t="inlineStr">
+        <is>
+          <t>P07 OK.</t>
+        </is>
+      </c>
+      <c r="L68" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M68" s="18" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="15" customHeight="1" s="12">
+      <c r="A69" s="17" t="inlineStr">
+        <is>
+          <t>E4-18</t>
+        </is>
+      </c>
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="C69" s="17" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D69" s="17" t="inlineStr">
+        <is>
+          <t>Consecutivos - no pertenecen al código</t>
+        </is>
+      </c>
+      <c r="E69" s="17" t="inlineStr">
+        <is>
+          <t>Modificación de artículos</t>
+        </is>
+      </c>
+      <c r="F69" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="17" t="inlineStr">
+        <is>
+          <t>QZX-99, QZ 77, QZ77 frente al código QZ.</t>
+        </is>
+      </c>
+      <c r="H69" s="17" t="inlineStr">
+        <is>
+          <t>No cuentan para QZ.</t>
+        </is>
+      </c>
+      <c r="I69" s="17" t="inlineStr">
+        <is>
+          <t>P07 casos R11–R13</t>
+        </is>
+      </c>
+      <c r="J69" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K69" s="18" t="inlineStr">
+        <is>
+          <t>P07 OK.</t>
+        </is>
+      </c>
+      <c r="L69" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M69" s="18" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1" s="12">
+      <c r="A70" s="17" t="inlineStr">
+        <is>
+          <t>E4-19</t>
+        </is>
+      </c>
+      <c r="B70" s="17" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="C70" s="17" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D70" s="17" t="inlineStr">
+        <is>
+          <t>Consecutivos - no conformes</t>
+        </is>
+      </c>
+      <c r="E70" s="17" t="inlineStr">
+        <is>
+          <t>Modificación de artículos</t>
+        </is>
+      </c>
+      <c r="F70" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="17" t="inlineStr">
+        <is>
+          <t>QZ-, QZ-ABC, QZ--5, QZ-12345.</t>
+        </is>
+      </c>
+      <c r="H70" s="17" t="inlineStr">
+        <is>
+          <t>No cuentan; se listan con su motivo.</t>
+        </is>
+      </c>
+      <c r="I70" s="17" t="inlineStr">
+        <is>
+          <t>P07 casos R04–R06, R16–R18</t>
+        </is>
+      </c>
+      <c r="J70" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K70" s="18" t="inlineStr">
+        <is>
+          <t>P07 OK.</t>
+        </is>
+      </c>
+      <c r="L70" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M70" s="18" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1" s="12">
+      <c r="A71" s="17" t="inlineStr">
+        <is>
+          <t>E4-20</t>
+        </is>
+      </c>
+      <c r="B71" s="17" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="C71" s="17" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D71" s="17" t="inlineStr">
+        <is>
+          <t>Consecutivos - paso de 999 a 1000</t>
+        </is>
+      </c>
+      <c r="E71" s="17" t="inlineStr">
+        <is>
+          <t>Modificación de artículos</t>
+        </is>
+      </c>
+      <c r="F71" s="17" t="inlineStr">
+        <is>
+          <t>Usado 998</t>
+        </is>
+      </c>
+      <c r="G71" s="17" t="inlineStr">
+        <is>
+          <t>Generar 3.</t>
+        </is>
+      </c>
+      <c r="H71" s="17" t="inlineStr">
+        <is>
+          <t>999, 1000, 1001 (4 dígitos sin ceros).</t>
+        </is>
+      </c>
+      <c r="I71" s="17" t="inlineStr">
+        <is>
+          <t>P07 caso D01</t>
+        </is>
+      </c>
+      <c r="J71" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K71" s="18" t="inlineStr">
+        <is>
+          <t>P07 OK.</t>
+        </is>
+      </c>
+      <c r="L71" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M71" s="18" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="15" customHeight="1" s="12">
+      <c r="A72" s="17" t="inlineStr">
+        <is>
+          <t>E4-21</t>
+        </is>
+      </c>
+      <c r="B72" s="17" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="C72" s="17" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D72" s="17" t="inlineStr">
+        <is>
+          <t>Consecutivos - tope 9999</t>
+        </is>
+      </c>
+      <c r="E72" s="17" t="inlineStr">
+        <is>
+          <t>Modificación de artículos</t>
+        </is>
+      </c>
+      <c r="F72" s="17" t="inlineStr">
+        <is>
+          <t>Usado 9998</t>
+        </is>
+      </c>
+      <c r="G72" s="17" t="inlineStr">
+        <is>
+          <t>Generar 3; luego 1.</t>
+        </is>
+      </c>
+      <c r="H72" s="17" t="inlineStr">
+        <is>
+          <t>Rechaza: "llega como máximo a …-9999: solo se pueden generar 1 consecutivo(s) más." sin generar; con 1 genera …-9999.</t>
+        </is>
+      </c>
+      <c r="I72" s="17" t="inlineStr">
+        <is>
+          <t>P08 caso T01</t>
+        </is>
+      </c>
+      <c r="J72" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K72" s="18" t="inlineStr">
+        <is>
+          <t>P08 y pantalla P19/P20 OK.</t>
+        </is>
+      </c>
+      <c r="L72" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M72" s="18" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="15" customHeight="1" s="12">
+      <c r="A73" s="17" t="inlineStr">
+        <is>
+          <t>E4-22</t>
+        </is>
+      </c>
+      <c r="B73" s="17" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="C73" s="17" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D73" s="17" t="inlineStr">
+        <is>
+          <t>Consecutivos - artículo fuera de lo sugerido</t>
+        </is>
+      </c>
+      <c r="E73" s="17" t="inlineStr">
+        <is>
+          <t>Modificación de artículos</t>
+        </is>
+      </c>
+      <c r="F73" s="17" t="inlineStr">
+        <is>
+          <t>Sugerencias 001–005</t>
+        </is>
+      </c>
+      <c r="G73" s="17" t="inlineStr">
+        <is>
+          <t>Crear artículos con QY-002, QY-003-ROJO, QY4, QY-050, QY-5, QY-ESPECIAL; Consultar/Generar.</t>
+        </is>
+      </c>
+      <c r="H73" s="17" t="inlineStr">
+        <is>
+          <t>002, 003 y 005 salen; QY4 no cuenta; tras QY-050 la siguiente es 051; QY-ESPECIAL no afecta.</t>
+        </is>
+      </c>
+      <c r="I73" s="17" t="inlineStr">
+        <is>
+          <t>P07 casos G06–G12</t>
+        </is>
+      </c>
+      <c r="J73" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K73" s="18" t="inlineStr">
+        <is>
+          <t>P07 OK. Comportamiento documentado en el manual (sugerencias).</t>
+        </is>
+      </c>
+      <c r="L73" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M73" s="18" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="15" customHeight="1" s="12">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t>E4-23</t>
+        </is>
+      </c>
+      <c r="B74" s="17" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="C74" s="17" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D74" s="17" t="inlineStr">
+        <is>
+          <t>Consecutivos - validaciones en BD</t>
+        </is>
+      </c>
+      <c r="E74" s="17" t="inlineStr">
+        <is>
+          <t>Modificación de artículos</t>
+        </is>
+      </c>
+      <c r="F74" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="17" t="inlineStr">
+        <is>
+          <t>SP con código vacío, NULL, 6 caracteres, guion, _, %, dos espacios, punto; cantidad 0, -1, 1001, NULL.</t>
+        </is>
+      </c>
+      <c r="H74" s="17" t="inlineStr">
+        <is>
+          <t>Cada uno rechaza con su mensaje y no crea códigos.</t>
+        </is>
+      </c>
+      <c r="I74" s="17" t="inlineStr">
+        <is>
+          <t>P08 casos V01–V13</t>
+        </is>
+      </c>
+      <c r="J74" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K74" s="18" t="inlineStr">
+        <is>
+          <t>P08 OK.</t>
+        </is>
+      </c>
+      <c r="L74" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M74" s="18" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="15" customHeight="1" s="12">
+      <c r="A75" s="17" t="inlineStr">
+        <is>
+          <t>E4-24</t>
+        </is>
+      </c>
+      <c r="B75" s="17" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="C75" s="17" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="D75" s="17" t="inlineStr">
+        <is>
+          <t>Consecutivos - aviso de sugerencias</t>
+        </is>
+      </c>
+      <c r="E75" s="17" t="inlineStr">
+        <is>
+          <t>Modificación de artículos</t>
+        </is>
+      </c>
+      <c r="F75" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="17" t="inlineStr">
+        <is>
+          <t>Abrir la pantalla.</t>
+        </is>
+      </c>
+      <c r="H75" s="17" t="inlineStr">
+        <is>
+          <t>Aviso "Los consecutivos son sugerencias".</t>
+        </is>
+      </c>
+      <c r="I75" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J75" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K75" s="18" t="inlineStr">
+        <is>
+          <t>Pantalla P01 OK.</t>
+        </is>
+      </c>
+      <c r="L75" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M75" s="18" t="inlineStr">
         <is>
           <t>24/10/2026</t>
         </is>
@@ -4930,68 +5600,68 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Pedidos T24</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>39471 cancelado; 39472 No; 39473 creado Sí y editado a No; 39474 Sí desde reserva 92 (reserva en estado 11)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>Documentar en el cierre</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Artículos E4 (copia de VA-196)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>ITEM_ID 13484 MU-452, 13485 ZY-5, 13486 ZX-25X y los de MU-453-2 y ZV-40-1 (nombre 'PRUEBA E4 ...')</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>Eliminar al cierre</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Consecutivos E4</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>ZZ-001..003; MU-454..456; MUX-001; ZY-006; ZX-001; ZV-041 (y códigos en INTERNAL_REFERENCE_CODES)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>Eliminar al cierre</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Respaldo script 18</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>8 filas en RQM_LOGS_OBJECT_BACKUP de los SP de reportes de pedidos (definición original)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>Conservar (lo usa la reversa)</t>
         </is>

--- a/documentos/2026-10-20 RQM Complemento de Modúlo de consulta de logs/T29 - Casos de prueba.xlsx
+++ b/documentos/2026-10-20 RQM Complemento de Modúlo de consulta de logs/T29 - Casos de prueba.xlsx
@@ -2588,17 +2588,17 @@
       </c>
       <c r="J37" s="18" t="inlineStr">
         <is>
-          <t>Corrección</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K37" s="18" t="inlineStr">
         <is>
-          <t>Bloqueado por script 18: falla con 'Incorrect syntax near +' (EXEC #RQM_T26_APPLY recibe expresiones con + CHAR(13)... como argumentos; T-SQL no lo permite). No alteró ningún SP (solo insertó los 8 respaldos). La app falla al abrir el reporte: SqlException 8145 '@IsSpecialOrder is not a parameter for procedure SP_GET_CUSTOMER_ORDER_REPORT'.</t>
+          <t>BD de pruebas restaurada; ~10% de pedidos marcados como especiales en la copia local. Fecha de pedido 16/07/2025: Todos 152 (Sí 15/No 137), Sí 15, No 137 = BD; resumen con la condición; dato por pedido. Contenido de impresión/PDF: condición + 15 pedidos. SP: Sí+No=Todos en jul-2025 (6.263 filas).</t>
         </is>
       </c>
       <c r="L37" s="18" t="inlineStr">
         <is>
-          <t>Claude App</t>
+          <t>Claude (nube)</t>
         </is>
       </c>
       <c r="M37" s="18" t="inlineStr">
@@ -2655,17 +2655,17 @@
       </c>
       <c r="J38" s="18" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K38" s="18" t="inlineStr">
         <is>
-          <t>Bloqueado por E3-13 (script 18).</t>
+          <t>BD de pruebas restaurada; ~10% de pedidos marcados como especiales en la copia local. Jul-2025: Todos 66, Sí 6, No 60 = BD; resumen y dato por pedido; impresión/PDF OK.</t>
         </is>
       </c>
       <c r="L38" s="18" t="inlineStr">
         <is>
-          <t>Claude App</t>
+          <t>Claude (nube)</t>
         </is>
       </c>
       <c r="M38" s="18" t="inlineStr">
@@ -2722,17 +2722,17 @@
       </c>
       <c r="J39" s="18" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K39" s="18" t="inlineStr">
         <is>
-          <t>Bloqueado por E3-13 (script 18).</t>
+          <t>BD de pruebas restaurada; ~10% de pedidos marcados como especiales en la copia local. 16/07/2025: Todos 152, Sí 15, No 137 = BD; resumen y dato por pedido; impresión/PDF OK.</t>
         </is>
       </c>
       <c r="L39" s="18" t="inlineStr">
         <is>
-          <t>Claude App</t>
+          <t>Claude (nube)</t>
         </is>
       </c>
       <c r="M39" s="18" t="inlineStr">
@@ -2789,17 +2789,17 @@
       </c>
       <c r="J40" s="18" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K40" s="18" t="inlineStr">
         <is>
-          <t>Bloqueado por E3-13 (script 18).</t>
+          <t>BD de pruebas restaurada; ~10% de pedidos marcados como especiales en la copia local. 16/07/2025: Todos 152, Sí 15, No 137 = BD; resumen y dato por pedido; impresión/PDF OK.</t>
         </is>
       </c>
       <c r="L40" s="18" t="inlineStr">
         <is>
-          <t>Claude App</t>
+          <t>Claude (nube)</t>
         </is>
       </c>
       <c r="M40" s="18" t="inlineStr">
@@ -2856,17 +2856,17 @@
       </c>
       <c r="J41" s="18" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K41" s="18" t="inlineStr">
         <is>
-          <t>Bloqueado por E3-13 (script 18).</t>
+          <t>BD de pruebas restaurada; ~10% de pedidos marcados como especiales en la copia local. Jul-2025: 230 pares documento-pedido (un pedido aparece bajo cada OC/traslado que le asignó), Sí 25, No 205 = BD; impresión/PDF OK. Corregidos 4 mensajes de validación de fechas que no correspondían a su campo (preexistente).</t>
         </is>
       </c>
       <c r="L41" s="18" t="inlineStr">
         <is>
-          <t>Claude App</t>
+          <t>Claude (nube)</t>
         </is>
       </c>
       <c r="M41" s="18" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="J42" s="18" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K42" s="18" t="inlineStr">
         <is>
-          <t>Bloqueado por E3-13 (script 18).</t>
+          <t>BD de pruebas restaurada; ~10% de pedidos marcados como especiales en la copia local. Pedidos jul-2025: Todos 18, Sí 3, No 15 = BD; resumen y dato por pedido. La pantalla no tiene acción de impresión/PDF.</t>
         </is>
       </c>
       <c r="L42" s="18" t="inlineStr">
         <is>
-          <t>Claude App</t>
+          <t>Claude (nube)</t>
         </is>
       </c>
       <c r="M42" s="18" t="inlineStr">
@@ -2990,17 +2990,17 @@
       </c>
       <c r="J43" s="18" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K43" s="18" t="inlineStr">
         <is>
-          <t>Bloqueado por E3-13 (script 18).</t>
+          <t>SP con fecha de pedido + cliente y con fecha estimada inicial y final: sin error. La pantalla exige inicial y final juntas.</t>
         </is>
       </c>
       <c r="L43" s="18" t="inlineStr">
         <is>
-          <t>Claude App</t>
+          <t>Claude (nube)</t>
         </is>
       </c>
       <c r="M43" s="18" t="inlineStr">
@@ -3057,17 +3057,17 @@
       </c>
       <c r="J44" s="18" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K44" s="18" t="inlineStr">
         <is>
-          <t>Bloqueado por E3-13 (script 18).</t>
+          <t>Pendientes de traslado: cliente (42 de 102), estado (78), fecha de pedido (8), fecha de proceso (7), fecha estimada (7) y referencia + cliente (1): todas las filas cumplen el filtro; sin error de coma doble.</t>
         </is>
       </c>
       <c r="L44" s="18" t="inlineStr">
         <is>
-          <t>Claude App</t>
+          <t>Claude (nube)</t>
         </is>
       </c>
       <c r="M44" s="18" t="inlineStr">
@@ -3124,17 +3124,17 @@
       </c>
       <c r="J45" s="18" t="inlineStr">
         <is>
-          <t>Corrección</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K45" s="18" t="inlineStr">
         <is>
-          <t>/export/AldebaranDb/customer-order/excel responde 500: InvalidOperationException 'The required column IsSpecialOrder was not present in the results of a FromSql operation' (script 18 no aplicado).</t>
+          <t>Excel y CSV de Pedidos (Sí 15 / Todos 152 / No 137 pedidos) y Back order (Sí 6 / No 60) = BD; columna "Pedido especial"; respetan filtros; encabezado "Observaciones Internas". Corregido (preexistente): el CSV no ponía entre comillas los valores con coma o salto de línea (teléfonos "310…,263…", observaciones en varias líneas) y se corrían las columnas; ahora cumple RFC 4180 (prueba unitaria).</t>
         </is>
       </c>
       <c r="L45" s="18" t="inlineStr">
         <is>
-          <t>Claude App</t>
+          <t>Claude (nube)</t>
         </is>
       </c>
       <c r="M45" s="18" t="inlineStr">
@@ -3191,17 +3191,17 @@
       </c>
       <c r="J46" s="18" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K46" s="18" t="inlineStr">
         <is>
-          <t>Sin sesión: redirige (opaqueredirect) = pide login OK. Con ?OrderNumber=1' OR '1'='1: 500 por el script 18 (no se pudo validar). Observación: el 500 devuelve el stack trace en texto plano al navegador.</t>
+          <t>Sin sesión: 302 a /Account/Login (Pedidos y Back order). Con sesión ?OrderNumber=1' OR '1'='1: 200 con solo el encabezado (no trae pedidos ni ejecuta nada). El stack trace en texto plano solo aparece en modo Development; en producción aplica UseExceptionHandler("/Error").</t>
         </is>
       </c>
       <c r="L46" s="18" t="inlineStr">
         <is>
-          <t>Claude App</t>
+          <t>Claude (nube)</t>
         </is>
       </c>
       <c r="M46" s="18" t="inlineStr">
@@ -5472,7 +5472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="30" customWidth="1" style="11" min="1" max="1"/>
@@ -5664,6 +5664,23 @@
       <c r="C11" s="11" t="inlineStr">
         <is>
           <t>Conservar (lo usa la reversa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Pedidos especiales (solo copia local de Claude)</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>En la copia de la BD restaurada en la nube se marcaron como especiales los pedidos con CUSTOMER_ORDER_ID terminado en 3 (3.949). No afecta la BD de pruebas del equipo de Andrés.</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/documentos/2026-10-20 RQM Complemento de Modúlo de consulta de logs/T29 - Casos de prueba.xlsx
+++ b/documentos/2026-10-20 RQM Complemento de Modúlo de consulta de logs/T29 - Casos de prueba.xlsx
@@ -521,14 +521,14 @@
     <row r="1" ht="17.35" customHeight="1" s="12">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>RQM Complemento módulo de Consulta de Logs + Marca de Oferta – T29 Casos de prueba</t>
+          <t>RQM Complemento Consulta de Logs, Marca $ BOMBA, Pedido especial y Generador de consecutivos – T29 Casos de prueba</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="12">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Rama: RQM-ComplementoLogs+SaleOff · BD de pruebas: GML0999\SQLEXPRESS01 · Sitio: https://localhost:6001 · Usuario: admin</t>
+          <t>Una sola entrega con los 4 requerimientos · Rama: RQM-ComplementoLogs+SaleOff · BD de pruebas: GML0999\SQLEXPRESS01 · Sitio: https://localhost:6001</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
     <row r="5" ht="15" customHeight="1" s="12">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>1. Ejecutar los scripts de Despliegue en orden (01–19) en la BD de pruebas antes de iniciar.</t>
+          <t>1. Ejecutar los scripts de Despliegue en orden (01–20) en la BD de pruebas antes de iniciar.</t>
         </is>
       </c>
     </row>
@@ -583,14 +583,14 @@
     <row r="11" ht="15" customHeight="1" s="12">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>Casos E1/E2 armados desde el plan de trabajo y los commits de la rama; contrastar con el detalle del Proyecto 'Desarrollos Promos Aldebaran' y completar si falta algo.</t>
+          <t>Columna Requerimiento: Logs, Marca $ BOMBA, Pedido especial o Generador de consecutivos. Los ID (E1-…, E4-…) se conservan como identificadores de caso.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>Fila de ejemplo de llenado: ID E3-01 → Resultado: OK · Observaciones: 'Conteo 12 = BD' · Probado por: Claude Chat · Fecha: 2026-10-25</t>
+          <t>Ejecución integral: 25/10/2026 en la nube (BD de pruebas restaurada): 72 OK; pendientes E1-16 y E3-12 (correo) para validar en local.</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" style="11" min="1" max="1"/>
-    <col width="8" customWidth="1" style="11" min="2" max="2"/>
+    <col width="24" customWidth="1" style="11" min="2" max="2"/>
     <col width="10" customWidth="1" style="11" min="3" max="3"/>
     <col width="32" customWidth="1" style="11" min="4" max="4"/>
     <col width="18" customWidth="1" style="11" min="5" max="5"/>
@@ -632,7 +632,7 @@
       </c>
       <c r="B1" s="16" t="inlineStr">
         <is>
-          <t>Entrega</t>
+          <t>Requerimiento</t>
         </is>
       </c>
       <c r="C1" s="16" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="B2" s="17" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="C2" s="17" t="inlineStr">
@@ -737,10 +737,26 @@
           <t>SELECT name FROM sys.indexes WHERE name IN ('IX_Logs_TimeStamp','IX_Logs_Template_TimeStamp','IX_track_Entity_Date','IX_track_Entity_Key'); -- 4 filas</t>
         </is>
       </c>
-      <c r="J2" s="18" t="n"/>
-      <c r="K2" s="18" t="n"/>
-      <c r="L2" s="18" t="n"/>
-      <c r="M2" s="18" t="n"/>
+      <c r="J2" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K2" s="18" t="inlineStr">
+        <is>
+          <t>BD de pruebas restaurada en la nube. Script 01 ejecutado 2 veces sin errores; 4 índices presentes. P01 (rendimiento) ejecutado sin errores.</t>
+        </is>
+      </c>
+      <c r="L2" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M2" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="35.05" customHeight="1" s="12">
       <c r="A3" s="17" t="inlineStr">
@@ -750,7 +766,7 @@
       </c>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="C3" s="17" t="inlineStr">
@@ -788,10 +804,26 @@
           <t>SELECT TOP 5 * FROM log.Logs ORDER BY TimeStamp DESC; SELECT TOP 5 * FROM log.track ORDER BY 1 DESC;</t>
         </is>
       </c>
-      <c r="J3" s="18" t="n"/>
-      <c r="K3" s="18" t="n"/>
-      <c r="L3" s="18" t="n"/>
-      <c r="M3" s="18" t="n"/>
+      <c r="J3" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K3" s="18" t="inlineStr">
+        <is>
+          <t>BD de pruebas restaurada en la nube. Durante toda la prueba log.Logs y log.track siguieron escribiendo (pedidos, reservas, OC, conexiones); errores controlados registrados en el Log general.</t>
+        </is>
+      </c>
+      <c r="L3" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M3" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="46.25" customHeight="1" s="12">
       <c r="A4" s="17" t="inlineStr">
@@ -801,7 +833,7 @@
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="C4" s="17" t="inlineStr">
@@ -839,10 +871,26 @@
           <t>SELECT TOP 10 * FROM log.track WHERE ENTITY_NAME LIKE '%Connection%' OR ENTITY_NAME LIKE '%NotificationProvider%' ORDER BY 1 DESC;</t>
         </is>
       </c>
-      <c r="J4" s="18" t="n"/>
-      <c r="K4" s="18" t="n"/>
-      <c r="L4" s="18" t="n"/>
-      <c r="M4" s="18" t="n"/>
+      <c r="J4" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K4" s="18" t="inlineStr">
+        <is>
+          <t>BD de pruebas restaurada en la nube. Contraseña cambiada en la conexión del autómata y en el SMTP: Track guarda "******** (modificada)"; FTP con movimiento ya enmascarado; la clave de prueba aparece 0 veces en log.track.</t>
+        </is>
+      </c>
+      <c r="L4" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M4" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="23.85" customHeight="1" s="12">
       <c r="A5" s="17" t="inlineStr">
@@ -852,7 +900,7 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
@@ -890,10 +938,26 @@
           <t>Buscar en log.track textos de clave conocidos (ej. clave SMTP anterior): 0 filas.</t>
         </is>
       </c>
-      <c r="J5" s="18" t="n"/>
-      <c r="K5" s="18" t="n"/>
-      <c r="L5" s="18" t="n"/>
-      <c r="M5" s="18" t="n"/>
+      <c r="J5" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K5" s="18" t="inlineStr">
+        <is>
+          <t>Corregido el script 02: la verificación final (EXISTS dentro de SUM, Msg 130) impedía ejecutar todo el lote. Ejecutado 2 veces: 0 contraseñas sin ofuscar.</t>
+        </is>
+      </c>
+      <c r="L5" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M5" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="57.45" customHeight="1" s="12">
       <c r="A6" s="17" t="inlineStr">
@@ -903,7 +967,7 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
@@ -941,10 +1005,26 @@
           <t>Scripts\Pruebas 04 - Pruebas T2 Track.sql</t>
         </is>
       </c>
-      <c r="J6" s="18" t="n"/>
-      <c r="K6" s="18" t="n"/>
-      <c r="L6" s="18" t="n"/>
-      <c r="M6" s="18" t="n"/>
+      <c r="J6" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K6" s="18" t="inlineStr">
+        <is>
+          <t>Las 19 entidades nuevas con ITrackeable tienen movimientos en log.track (22/10 a 25/10); P02 sin credenciales en claro.</t>
+        </is>
+      </c>
+      <c r="L6" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M6" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="23.85" customHeight="1" s="12">
       <c r="A7" s="17" t="inlineStr">
@@ -954,7 +1034,7 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
@@ -984,7 +1064,7 @@
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>10 tipos; rango obligatorio; paginación con total.</t>
+          <t>10 tipos; rango obligatorio; solo alarmas con al menos una visualización; filtro @EmployeeId; paginación con total.</t>
         </is>
       </c>
       <c r="I7" s="17" t="inlineStr">
@@ -992,10 +1072,26 @@
           <t>Pruebas P03 (21 casos)</t>
         </is>
       </c>
-      <c r="J7" s="18" t="n"/>
-      <c r="K7" s="18" t="n"/>
-      <c r="L7" s="18" t="n"/>
-      <c r="M7" s="18" t="n"/>
+      <c r="J7" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K7" s="18" t="inlineStr">
+        <is>
+          <t>P03 actualizado a la regla nueva (solo alarmas visualizadas, filtro por empleado): 23/23 OK.</t>
+        </is>
+      </c>
+      <c r="L7" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M7" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="46.25" customHeight="1" s="12">
       <c r="A8" s="17" t="inlineStr">
@@ -1005,7 +1101,7 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
@@ -1043,10 +1139,26 @@
           <t>SELECT TOP 20 * FROM dbo.INVENTORY_ALARM_LOG ORDER BY 1 DESC;</t>
         </is>
       </c>
-      <c r="J8" s="18" t="n"/>
-      <c r="K8" s="18" t="n"/>
-      <c r="L8" s="18" t="n"/>
-      <c r="M8" s="18" t="n"/>
+      <c r="J8" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K8" s="18" t="inlineStr">
+        <is>
+          <t>P04 (transacción revertida): refresco por comprometido, OC que cubre el mínimo, inactivación por ingreso y bodega local/sin stock: 11/11 OK. P04 corregido (DECLARE de tabla con escalares).</t>
+        </is>
+      </c>
+      <c r="L8" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M8" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="35.05" customHeight="1" s="12">
       <c r="A9" s="17" t="inlineStr">
@@ -1056,7 +1168,7 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
@@ -1094,10 +1206,26 @@
           <t>INVENTORY_ALARM_LOG con ALARM_TYPE_CODE = 'MINIMUM_LOCAL_WAREHOUSE'</t>
         </is>
       </c>
-      <c r="J9" s="18" t="n"/>
-      <c r="K9" s="18" t="n"/>
-      <c r="L9" s="18" t="n"/>
-      <c r="M9" s="18" t="n"/>
+      <c r="J9" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K9" s="18" t="inlineStr">
+        <is>
+          <t>P04 L1–L3: movimiento en Zona Franca sin efecto, refresco y alcance del mínimo en Bodega Local; log con origen.</t>
+        </is>
+      </c>
+      <c r="L9" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M9" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="23.85" customHeight="1" s="12">
       <c r="A10" s="17" t="inlineStr">
@@ -1107,7 +1235,7 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
@@ -1145,10 +1273,26 @@
           <t>Pruebas P04 (J1–J3)</t>
         </is>
       </c>
-      <c r="J10" s="18" t="n"/>
-      <c r="K10" s="18" t="n"/>
-      <c r="L10" s="18" t="n"/>
-      <c r="M10" s="18" t="n"/>
+      <c r="J10" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K10" s="18" t="inlineStr">
+        <is>
+          <t>Job "Verificacion Alarmas" creado en el SQL Server de pruebas; script 05 aplicado 2 veces; ejecución real del job: pasos OK, 2 inactivaciones con origen "Proceso programado - depuración", sin refrescos sin cambio. Validar en producción el permiso sobre msdb.</t>
+        </is>
+      </c>
+      <c r="L10" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M10" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="23.85" customHeight="1" s="12">
       <c r="A11" s="17" t="inlineStr">
@@ -1158,7 +1302,7 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
@@ -1183,12 +1327,12 @@
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>Abrir cada contexto; filtrar por fechas y texto; abrir el diálogo de visualizaciones. Abrir un contexto sin rol.</t>
+          <t>Abrir cada contexto; filtrar por fechas, empleado y texto; expandir una alarma. Abrir un contexto sin rol.</t>
         </is>
       </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t>Totales = SP; diálogo con quién y cuándo visualizó. Sin rol: /unauthorized.</t>
+          <t>Solo alarmas visualizadas; totales = SP; al expandir, empleados que la visualizaron con área y fecha. Sin rol: /unauthorized.</t>
         </is>
       </c>
       <c r="I11" s="17" t="inlineStr">
@@ -1196,10 +1340,26 @@
           <t>Pruebas P05</t>
         </is>
       </c>
-      <c r="J11" s="18" t="n"/>
-      <c r="K11" s="18" t="n"/>
-      <c r="L11" s="18" t="n"/>
-      <c r="M11" s="18" t="n"/>
+      <c r="J11" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K11" s="18" t="inlineStr">
+        <is>
+          <t>10 tipos en 4 contextos = SP. Ajuste pedido por Andrés: solo alarmas visualizadas, filtro Empleado (Eseban 304 / Gustavo 417 = BD) y subgrilla con empleado, área y fecha al expandir. Sin rol: R-07.</t>
+        </is>
+      </c>
+      <c r="L11" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M11" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="35.05" customHeight="1" s="12">
       <c r="A12" s="17" t="inlineStr">
@@ -1209,7 +1369,7 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
@@ -1247,10 +1407,26 @@
           <t>SELECT COUNT(*) FROM dbo.INVENTORY_ALARM_LOG WHERE EVENT_DATE BETWEEN ...</t>
         </is>
       </c>
-      <c r="J12" s="18" t="n"/>
-      <c r="K12" s="18" t="n"/>
-      <c r="L12" s="18" t="n"/>
-      <c r="M12" s="18" t="n"/>
+      <c r="J12" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K12" s="18" t="inlineStr">
+        <is>
+          <t>Todos 9 / cantidades mínimas 8 / + inactivación 6 = BD; estado anterior → nuevo y origen.</t>
+        </is>
+      </c>
+      <c r="L12" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M12" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="35.05" customHeight="1" s="12">
       <c r="A13" s="17" t="inlineStr">
@@ -1260,7 +1436,7 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
@@ -1298,10 +1474,26 @@
           <t>Pruebas P06</t>
         </is>
       </c>
-      <c r="J13" s="18" t="n"/>
-      <c r="K13" s="18" t="n"/>
-      <c r="L13" s="18" t="n"/>
-      <c r="M13" s="18" t="n"/>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K13" s="18" t="inlineStr">
+        <is>
+          <t>Búsqueda por pedido 39471 sin entidad: 8 movimientos de Pedido, Detalle, Pedido cancelado y modificado = LOG_TRACK_OBJECTS; detalle con anterior/nuevo y descripción de Ids (Referencia "[VA-196] Abanico - Azul", Cliente). P06 corregido y 7/7 OK.</t>
+        </is>
+      </c>
+      <c r="L13" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M13" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="35.05" customHeight="1" s="12">
       <c r="A14" s="17" t="inlineStr">
@@ -1311,7 +1503,7 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
@@ -1349,10 +1541,26 @@
           <t>SELECT * FROM dbo.LOG_TRACK_FIELD_NAMES WHERE FIELD_NAME IN ('IsSpecialOrder','IsBombPrice');</t>
         </is>
       </c>
-      <c r="J14" s="18" t="n"/>
-      <c r="K14" s="18" t="n"/>
-      <c r="L14" s="18" t="n"/>
-      <c r="M14" s="18" t="n"/>
+      <c r="J14" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K14" s="18" t="inlineStr">
+        <is>
+          <t>Campos en español (Pedido especial, Cliente, Observaciones…); campos técnicos ocultos por defecto. Corregido: booleanos se mostraban True/False, ahora Sí/No (prueba unitaria).</t>
+        </is>
+      </c>
+      <c r="L14" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M14" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="35.05" customHeight="1" s="12">
       <c r="A15" s="17" t="inlineStr">
@@ -1362,7 +1570,7 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>Marca $ BOMBA</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
@@ -1400,10 +1608,26 @@
           <t>SELECT ITEM_NAME, IS_BOMB_PRICE, IS_SALE_OFF FROM items WHERE ITEM_ID = 2554;</t>
         </is>
       </c>
-      <c r="J15" s="18" t="n"/>
-      <c r="K15" s="18" t="n"/>
-      <c r="L15" s="18" t="n"/>
-      <c r="M15" s="18" t="n"/>
+      <c r="J15" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K15" s="18" t="inlineStr">
+        <is>
+          <t>MU-357: sufijo " - $ BOMBA"; Oferta desmarca Precio bomba y cambia el sufijo; mensaje si supera 50 caracteres; guardado y en Track.</t>
+        </is>
+      </c>
+      <c r="L15" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M15" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="23.85" customHeight="1" s="12">
       <c r="A16" s="17" t="inlineStr">
@@ -1413,7 +1637,7 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>Marca $ BOMBA</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
@@ -1451,10 +1675,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J16" s="18" t="n"/>
-      <c r="K16" s="18" t="n"/>
-      <c r="L16" s="18" t="n"/>
-      <c r="M16" s="18" t="n"/>
+      <c r="J16" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K16" s="18" t="inlineStr">
+        <is>
+          <t>HO-13 y ASTON-STY: etiqueta "$ BOMBA" en el diálogo de inventario (caso sin imagen: las imágenes están en el equipo de Andrés). Pendiente en local: caso con imagen.</t>
+        </is>
+      </c>
+      <c r="L16" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M16" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="23.85" customHeight="1" s="12">
       <c r="A17" s="17" t="inlineStr">
@@ -1464,7 +1704,7 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>Marca $ BOMBA</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
@@ -1502,10 +1742,26 @@
           <t>Pendiente desde E1: verificar el Excel recibido.</t>
         </is>
       </c>
-      <c r="J17" s="18" t="n"/>
-      <c r="K17" s="18" t="n"/>
-      <c r="L17" s="18" t="n"/>
-      <c r="M17" s="18" t="n"/>
+      <c r="J17" s="18" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K17" s="18" t="inlineStr">
+        <is>
+          <t>En la nube no hay SMTP saliente: lo valida Andrés en su equipo (Excel del correo con $ BOMBA sobre la imagen).</t>
+        </is>
+      </c>
+      <c r="L17" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M17" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="35.05" customHeight="1" s="12">
       <c r="A18" s="17" t="inlineStr">
@@ -1515,7 +1771,7 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
@@ -1553,10 +1809,26 @@
           <t>SELECT COUNT(*) FROM &lt;tabla de log&gt; WHERE fecha BETWEEN ...</t>
         </is>
       </c>
-      <c r="J18" s="18" t="n"/>
-      <c r="K18" s="18" t="n"/>
-      <c r="L18" s="18" t="n"/>
-      <c r="M18" s="18" t="n"/>
+      <c r="J18" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K18" s="18" t="inlineStr">
+        <is>
+          <t>Despachos 67/125, traslados 10.153/330 = BD; el número de pedido abre el detalle (con Pedido especial).</t>
+        </is>
+      </c>
+      <c r="L18" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M18" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="35.05" customHeight="1" s="12">
       <c r="A19" s="17" t="inlineStr">
@@ -1566,7 +1838,7 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
@@ -1604,10 +1876,26 @@
           <t>SELECT * FROM PURCHASE_ORDER_ADJUSTMENT_LOG WHERE PURCHASE_ORDER_ID IN (742,752);</t>
         </is>
       </c>
-      <c r="J19" s="18" t="n"/>
-      <c r="K19" s="18" t="n"/>
-      <c r="L19" s="18" t="n"/>
-      <c r="M19" s="18" t="n"/>
+      <c r="J19" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K19" s="18" t="inlineStr">
+        <is>
+          <t>6 solicitudes con resolución (Aprobada/Devuelta), quién y motivo. En esta BD no están las OC 742/752 de la referencia; estado correcto tras el script 15.</t>
+        </is>
+      </c>
+      <c r="L19" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M19" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="35.05" customHeight="1" s="12">
       <c r="A20" s="17" t="inlineStr">
@@ -1617,7 +1905,7 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
@@ -1655,10 +1943,26 @@
           <t>SELECT * FROM PURCHASE_ORDER_APPROVAL_RANGE_LOG ORDER BY 1 DESC;</t>
         </is>
       </c>
-      <c r="J20" s="18" t="n"/>
-      <c r="K20" s="18" t="n"/>
-      <c r="L20" s="18" t="n"/>
-      <c r="M20" s="18" t="n"/>
+      <c r="J20" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K20" s="18" t="inlineStr">
+        <is>
+          <t>351–400: 0,05 → 0,06 y demás cambios con valor anterior y nuevo.</t>
+        </is>
+      </c>
+      <c r="L20" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M20" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="23.85" customHeight="1" s="12">
       <c r="A21" s="17" t="inlineStr">
@@ -1668,7 +1972,7 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
@@ -1706,10 +2010,26 @@
           <t>SELECT COUNT(*) FROM log.Logs WHERE TimeStamp &gt;= ...</t>
         </is>
       </c>
-      <c r="J21" s="18" t="n"/>
-      <c r="K21" s="18" t="n"/>
-      <c r="L21" s="18" t="n"/>
-      <c r="M21" s="18" t="n"/>
+      <c r="J21" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K21" s="18" t="inlineStr">
+        <is>
+          <t>Oct-2026: 36 grupos, nivel Error 8 = SP; ocurrencias y detalle técnico (excepción) se abren.</t>
+        </is>
+      </c>
+      <c r="L21" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M21" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="35.05" customHeight="1" s="12">
       <c r="A22" s="17" t="inlineStr">
@@ -1719,7 +2039,7 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
@@ -1757,10 +2077,26 @@
           <t>SELECT TOP 10 * FROM log.Logs WHERE ... 'AutomataExistencias' ORDER BY TimeStamp DESC;</t>
         </is>
       </c>
-      <c r="J22" s="18" t="n"/>
-      <c r="K22" s="18" t="n"/>
-      <c r="L22" s="18" t="n"/>
-      <c r="M22" s="18" t="n"/>
+      <c r="J22" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K22" s="18" t="inlineStr">
+        <is>
+          <t>Simulado: llamadas a log.SP_INSERT_AUTOMATA_EXISTENCIAS_LOG (Info/Warn/Error) aparecen en el Log general con origen AutomataExistencias y su nivel. Pendiente en local: el autómata real con el NLog.config.</t>
+        </is>
+      </c>
+      <c r="L22" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M22" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="35.05" customHeight="1" s="12">
       <c r="A23" s="17" t="inlineStr">
@@ -1770,7 +2106,7 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
@@ -1808,10 +2144,26 @@
           <t>SELECT TOP 5 * FROM PURCHASE_ORDER_ADJUSTMENT_LOG ORDER BY 1 DESC;</t>
         </is>
       </c>
-      <c r="J23" s="18" t="n"/>
-      <c r="K23" s="18" t="n"/>
-      <c r="L23" s="18" t="n"/>
-      <c r="M23" s="18" t="n"/>
+      <c r="J23" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K23" s="18" t="inlineStr">
+        <is>
+          <t>Ajustes aprobados registrados como Confirmada (OC 744, 749), devueltos como Pendiente; ninguno en "En aprobación". OC nueva 0000000741 confirmada desde la pantalla.</t>
+        </is>
+      </c>
+      <c r="L23" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M23" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="35.05" customHeight="1" s="12">
       <c r="A24" s="17" t="inlineStr">
@@ -1821,7 +2173,7 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
@@ -1859,10 +2211,26 @@
           <t>SELECT * FROM visualized_minimum_quantity_alarms WHERE MINIMUM_QUANTITY_ALARM_ID = ...</t>
         </is>
       </c>
-      <c r="J24" s="18" t="n"/>
-      <c r="K24" s="18" t="n"/>
-      <c r="L24" s="18" t="n"/>
-      <c r="M24" s="18" t="n"/>
+      <c r="J24" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K24" s="18" t="inlineStr">
+        <is>
+          <t>OC 0000000526 editada solo en la proforma: alarma 15904 sigue activa, misma fecha, 2 visualizaciones, 0 eventos; modificación registrada.</t>
+        </is>
+      </c>
+      <c r="L24" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M24" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="23.85" customHeight="1" s="12">
       <c r="A25" s="17" t="inlineStr">
@@ -1872,7 +2240,7 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Marca $ BOMBA</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
@@ -1910,10 +2278,26 @@
           <t>Consultas de conteo por IS_ACTIVE, IS_BOMB_PRICE, etc.</t>
         </is>
       </c>
-      <c r="J25" s="18" t="n"/>
-      <c r="K25" s="18" t="n"/>
-      <c r="L25" s="18" t="n"/>
-      <c r="M25" s="18" t="n"/>
+      <c r="J25" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K25" s="18" t="inlineStr">
+        <is>
+          <t>10 condiciones: Sí + No = Todos en BD (7.551 referencias). En pantalla Precio bomba = Sí: solo ASTON-STY, HO-13 y MU-357 (28 referencias) y resumen "Precio bomba: Sí".</t>
+        </is>
+      </c>
+      <c r="L25" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M25" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="12">
       <c r="A26" s="17" t="inlineStr">
@@ -1923,7 +2307,7 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Marca $ BOMBA</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
@@ -1961,10 +2345,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J26" s="18" t="n"/>
-      <c r="K26" s="18" t="n"/>
-      <c r="L26" s="18" t="n"/>
-      <c r="M26" s="18" t="n"/>
+      <c r="J26" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K26" s="18" t="inlineStr">
+        <is>
+          <t>Precio bomba: Sí 27 + No 6.225 = 6.252 en BD; en pantalla resumen con la condición y solo artículos $ BOMBA.</t>
+        </is>
+      </c>
+      <c r="L26" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M26" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="23.85" customHeight="1" s="12">
       <c r="A27" s="17" t="inlineStr">
@@ -1974,7 +2374,7 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Marca $ BOMBA</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
@@ -2012,10 +2412,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J27" s="18" t="n"/>
-      <c r="K27" s="18" t="n"/>
-      <c r="L27" s="18" t="n"/>
-      <c r="M27" s="18" t="n"/>
+      <c r="J27" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K27" s="18" t="inlineStr">
+        <is>
+          <t>Valores iniciales Sí / Sí / Todos; jul-2025: Sí + No = Todos en las tres condiciones (24.868 movimientos).</t>
+        </is>
+      </c>
+      <c r="L27" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M27" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="23.85" customHeight="1" s="12">
       <c r="A28" s="17" t="inlineStr">
@@ -2025,7 +2441,7 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Marca $ BOMBA</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
@@ -2063,10 +2479,26 @@
           <t>Pendiente desde T22.</t>
         </is>
       </c>
-      <c r="J28" s="18" t="n"/>
-      <c r="K28" s="18" t="n"/>
-      <c r="L28" s="18" t="n"/>
-      <c r="M28" s="18" t="n"/>
+      <c r="J28" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K28" s="18" t="inlineStr">
+        <is>
+          <t>Abierto desde la alarma de HO-13: referencia fija (línea, artículo y referencia deshabilitados); las condiciones no se ofrecen porque no aplican.</t>
+        </is>
+      </c>
+      <c r="L28" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M28" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="35.05" customHeight="1" s="12">
       <c r="A29" s="17" t="inlineStr">
@@ -2076,7 +2508,7 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Pedido especial</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
@@ -2114,10 +2546,26 @@
           <t>SELECT COUNT(*) FROM customer_orders WHERE IS_SPECIAL_ORDER &lt;&gt; 0; -- 0 antes de crear especiales</t>
         </is>
       </c>
-      <c r="J29" s="18" t="n"/>
-      <c r="K29" s="18" t="n"/>
-      <c r="L29" s="18" t="n"/>
-      <c r="M29" s="18" t="n"/>
+      <c r="J29" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K29" s="18" t="inlineStr">
+        <is>
+          <t>Script 17 ejecutado 2 veces sin errores.</t>
+        </is>
+      </c>
+      <c r="L29" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M29" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="35.05" customHeight="1" s="12">
       <c r="A30" s="17" t="inlineStr">
@@ -2127,7 +2575,7 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Pedido especial</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
@@ -2165,10 +2613,26 @@
           <t>SELECT TOP 2 ORDER_NUMBER, IS_SPECIAL_ORDER FROM customer_orders ORDER BY 1 DESC;</t>
         </is>
       </c>
-      <c r="J30" s="18" t="n"/>
-      <c r="K30" s="18" t="n"/>
-      <c r="L30" s="18" t="n"/>
-      <c r="M30" s="18" t="n"/>
+      <c r="J30" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K30" s="18" t="inlineStr">
+        <is>
+          <t>Sin elegir: "Debe indicar si es un pedido especial"; Sí → "No, modificar" conserva lo digitado; "Sí, crear" graba 0000039475 con IS_SPECIAL_ORDER = 1.</t>
+        </is>
+      </c>
+      <c r="L30" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M30" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="23.85" customHeight="1" s="12">
       <c r="A31" s="17" t="inlineStr">
@@ -2178,7 +2642,7 @@
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Pedido especial</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
@@ -2216,10 +2680,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J31" s="18" t="n"/>
-      <c r="K31" s="18" t="n"/>
-      <c r="L31" s="18" t="n"/>
-      <c r="M31" s="18" t="n"/>
+      <c r="J31" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K31" s="18" t="inlineStr">
+        <is>
+          <t>Reserva 0000000093 creada y modificada; convertida en pedido 0000039476 (especial): obligatorio, confirmación, Tab fecha → Pedido especial → notas; reserva queda En Pedido.</t>
+        </is>
+      </c>
+      <c r="L31" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M31" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="23.85" customHeight="1" s="12">
       <c r="A32" s="17" t="inlineStr">
@@ -2229,7 +2709,7 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Pedido especial</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
@@ -2267,10 +2747,26 @@
           <t>SELECT IS_SPECIAL_ORDER FROM customer_orders WHERE ORDER_NUMBER = '...';</t>
         </is>
       </c>
-      <c r="J32" s="18" t="n"/>
-      <c r="K32" s="18" t="n"/>
-      <c r="L32" s="18" t="n"/>
-      <c r="M32" s="18" t="n"/>
+      <c r="J32" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K32" s="18" t="inlineStr">
+        <is>
+          <t>Editar solo notas: sin confirmación de Pedido especial; Sí → No: "Pedido especial cambia de SÍ a NO", "No, modificar" vuelve; "Sí, cambiar" graba; 2 registros en el log de modificaciones y Track True → False.</t>
+        </is>
+      </c>
+      <c r="L32" s="18" t="inlineStr">
+        <is>
+          <t>Claude (nube)</t>
+        </is>
+      </c>
+      <c r="M32" s="18" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="35.05" customHeight="1" s="12">
       <c r="A33" s="17" t="inlineStr">
@@ -2280,7 +2776,7 @@
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Pedido especial</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
@@ -2347,7 +2843,7 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Pedido especial</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
@@ -2414,7 +2910,7 @@
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Pedido especial</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
@@ -2459,17 +2955,17 @@
       </c>
       <c r="K35" s="18" t="inlineStr">
         <is>
-          <t>Resumen/imprimir del 39473 muestra 'Pedido especial: No' y 'Observaciones internas: Prueba T24 notas'. Correo enviado al cliente 79872389 (23/10 pedido 39473): falta revisar el PDF adjunto en el buzón. PDF de 'Acciones' no probado.</t>
+          <t>Imprimir/PDF verificados por la Claude App; falta revisar el PDF adjunto en el correo (sin SMTP en la nube): Andrés en local.</t>
         </is>
       </c>
       <c r="L35" s="18" t="inlineStr">
         <is>
-          <t>Claude App</t>
+          <t>Claude (nube)</t>
         </is>
       </c>
       <c r="M35" s="18" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>25/10/2026</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2977,7 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Pedido especial</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
@@ -2548,7 +3044,7 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Pedido especial</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
@@ -2615,7 +3111,7 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Pedido especial</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
@@ -2682,7 +3178,7 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Pedido especial</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
@@ -2749,7 +3245,7 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Pedido especial</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
@@ -2816,7 +3312,7 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Pedido especial</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
@@ -2883,7 +3379,7 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Pedido especial</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
@@ -2950,7 +3446,7 @@
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Pedido especial</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
@@ -3017,7 +3513,7 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Pedido especial</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
@@ -3084,7 +3580,7 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Pedido especial</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
@@ -3151,7 +3647,7 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Pedido especial</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
@@ -3218,7 +3714,7 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Pedido especial</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
@@ -3285,7 +3781,7 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Pedido especial</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
@@ -3352,7 +3848,7 @@
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Pedido especial</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
@@ -3419,7 +3915,7 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Pedido especial</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
@@ -3486,7 +3982,7 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Pedido especial</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
@@ -3526,22 +4022,22 @@
       </c>
       <c r="J51" s="18" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K51" s="18" t="inlineStr">
         <is>
-          <t>No hay pedido en proceso que se pueda cerrar (39467: 'Existen cantidades en proceso').</t>
+          <t>Pedido 0000038653 (especial) cerrado vía solicitud aprobada; el log de cierre lo muestra con Pedido especial: Sí.</t>
         </is>
       </c>
       <c r="L51" s="18" t="inlineStr">
         <is>
-          <t>Claude App</t>
+          <t>Claude (nube)</t>
         </is>
       </c>
       <c r="M51" s="18" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>25/10/2026</t>
         </is>
       </c>
     </row>
@@ -3553,7 +4049,7 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
@@ -3620,7 +4116,7 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
@@ -3687,7 +4183,7 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
@@ -3754,7 +4250,7 @@
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
@@ -3821,7 +4317,7 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
@@ -3888,7 +4384,7 @@
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
@@ -3955,7 +4451,7 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
@@ -4022,7 +4518,7 @@
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
@@ -4089,7 +4585,7 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
@@ -4156,7 +4652,7 @@
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
@@ -4223,7 +4719,7 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
@@ -4290,7 +4786,7 @@
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
@@ -4357,7 +4853,7 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="C64" s="17" t="inlineStr">
@@ -4424,7 +4920,7 @@
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="C65" s="17" t="inlineStr">
@@ -4491,7 +4987,7 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="C66" s="17" t="inlineStr">
@@ -4558,7 +5054,7 @@
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="C67" s="17" t="inlineStr">
@@ -4625,7 +5121,7 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
@@ -4692,7 +5188,7 @@
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="C69" s="17" t="inlineStr">
@@ -4759,7 +5255,7 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="C70" s="17" t="inlineStr">
@@ -4826,7 +5322,7 @@
       </c>
       <c r="B71" s="17" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="C71" s="17" t="inlineStr">
@@ -4893,7 +5389,7 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="C72" s="17" t="inlineStr">
@@ -4960,7 +5456,7 @@
       </c>
       <c r="B73" s="17" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="C73" s="17" t="inlineStr">
@@ -5027,7 +5523,7 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="C74" s="17" t="inlineStr">
@@ -5094,7 +5590,7 @@
       </c>
       <c r="B75" s="17" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="C75" s="17" t="inlineStr">
@@ -5329,7 +5825,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F4" s="18" t="n"/>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>Correo de mínimos: Andrés en local (sin SMTP en la nube).</t>
+        </is>
+      </c>
       <c r="G4" s="18" t="n"/>
       <c r="H4" s="18" t="n"/>
     </row>
@@ -5356,10 +5856,14 @@
       </c>
       <c r="E5" s="18" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F5" s="18" t="n"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>Pedido creado (39475), modificado, cancelado por solicitud aprobada; cierre de 38653; Track y logs con Pedido especial.</t>
+        </is>
+      </c>
       <c r="G5" s="18" t="n"/>
       <c r="H5" s="18" t="n"/>
     </row>
@@ -5386,10 +5890,14 @@
       </c>
       <c r="E6" s="18" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="n"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>OC creada (0000000741), modificada (0000000526), cancelada por solicitud aprobada y confirmada con cantidad recibida.</t>
+        </is>
+      </c>
       <c r="G6" s="18" t="n"/>
       <c r="H6" s="18" t="n"/>
     </row>
@@ -5416,10 +5924,14 @@
       </c>
       <c r="E7" s="18" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="n"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>Reserva 93 creada, modificada y pasada a pedido; reserva 94 cancelada.</t>
+        </is>
+      </c>
       <c r="G7" s="18" t="n"/>
       <c r="H7" s="18" t="n"/>
     </row>
@@ -5446,10 +5958,14 @@
       </c>
       <c r="E8" s="18" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="n"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>Usuario solo con Consulta de pedidos y Log de pedidos: menú solo Log de pedidos; 7 rutas de otros logs y Consecutivos → Unauthorized; 3 rutas de su rol permitidas.</t>
+        </is>
+      </c>
       <c r="G8" s="18" t="n"/>
       <c r="H8" s="18" t="n"/>
     </row>
@@ -5710,7 +6226,7 @@
     <row r="1" ht="15" customHeight="1" s="12">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>Entrega</t>
+          <t>Requerimiento</t>
         </is>
       </c>
       <c r="B1" s="16" t="inlineStr">
@@ -5752,27 +6268,27 @@
     <row r="2" ht="15" customHeight="1" s="12">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="B2" s="19">
-        <f>COUNTIF('Casos de prueba'!$B$2:$B$65,A2)</f>
+        <f>COUNTIF('Casos de prueba'!$B$2:$B$200,A2)</f>
         <v/>
       </c>
       <c r="C2" s="19">
-        <f>COUNTIFS('Casos de prueba'!$B$2:$B$65,$A2,'Casos de prueba'!$J$2:$J$65,"OK")</f>
+        <f>COUNTIFS('Casos de prueba'!$B$2:$B$200,$A2,'Casos de prueba'!$J$2:$J$200,"OK")</f>
         <v/>
       </c>
       <c r="D2" s="19">
-        <f>COUNTIFS('Casos de prueba'!$B$2:$B$65,$A2,'Casos de prueba'!$J$2:$J$65,"Corrección")</f>
+        <f>COUNTIFS('Casos de prueba'!$B$2:$B$200,$A2,'Casos de prueba'!$J$2:$J$200,"Corrección")</f>
         <v/>
       </c>
       <c r="E2" s="19">
-        <f>COUNTIFS('Casos de prueba'!$B$2:$B$65,$A2,'Casos de prueba'!$J$2:$J$65,"Pendiente")</f>
+        <f>COUNTIFS('Casos de prueba'!$B$2:$B$200,$A2,'Casos de prueba'!$J$2:$J$200,"Pendiente")</f>
         <v/>
       </c>
       <c r="F2" s="19">
-        <f>COUNTIFS('Casos de prueba'!$B$2:$B$65,$A2,'Casos de prueba'!$J$2:$J$65,"No aplica")</f>
+        <f>COUNTIFS('Casos de prueba'!$B$2:$B$200,$A2,'Casos de prueba'!$J$2:$J$200,"No aplica")</f>
         <v/>
       </c>
       <c r="G2" s="19">
@@ -5787,27 +6303,27 @@
     <row r="3" ht="15" customHeight="1" s="12">
       <c r="A3" s="19" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>Marca $ BOMBA</t>
         </is>
       </c>
       <c r="B3" s="19">
-        <f>COUNTIF('Casos de prueba'!$B$2:$B$65,A3)</f>
+        <f>COUNTIF('Casos de prueba'!$B$2:$B$200,A3)</f>
         <v/>
       </c>
       <c r="C3" s="19">
-        <f>COUNTIFS('Casos de prueba'!$B$2:$B$65,$A3,'Casos de prueba'!$J$2:$J$65,"OK")</f>
+        <f>COUNTIFS('Casos de prueba'!$B$2:$B$200,$A3,'Casos de prueba'!$J$2:$J$200,"OK")</f>
         <v/>
       </c>
       <c r="D3" s="19">
-        <f>COUNTIFS('Casos de prueba'!$B$2:$B$65,$A3,'Casos de prueba'!$J$2:$J$65,"Corrección")</f>
+        <f>COUNTIFS('Casos de prueba'!$B$2:$B$200,$A3,'Casos de prueba'!$J$2:$J$200,"Corrección")</f>
         <v/>
       </c>
       <c r="E3" s="19">
-        <f>COUNTIFS('Casos de prueba'!$B$2:$B$65,$A3,'Casos de prueba'!$J$2:$J$65,"Pendiente")</f>
+        <f>COUNTIFS('Casos de prueba'!$B$2:$B$200,$A3,'Casos de prueba'!$J$2:$J$200,"Pendiente")</f>
         <v/>
       </c>
       <c r="F3" s="19">
-        <f>COUNTIFS('Casos de prueba'!$B$2:$B$65,$A3,'Casos de prueba'!$J$2:$J$65,"No aplica")</f>
+        <f>COUNTIFS('Casos de prueba'!$B$2:$B$200,$A3,'Casos de prueba'!$J$2:$J$200,"No aplica")</f>
         <v/>
       </c>
       <c r="G3" s="19">
@@ -5822,27 +6338,27 @@
     <row r="4" ht="15" customHeight="1" s="12">
       <c r="A4" s="19" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>Pedido especial</t>
         </is>
       </c>
       <c r="B4" s="19">
-        <f>COUNTIF('Casos de prueba'!$B$2:$B$65,A4)</f>
+        <f>COUNTIF('Casos de prueba'!$B$2:$B$200,A4)</f>
         <v/>
       </c>
       <c r="C4" s="19">
-        <f>COUNTIFS('Casos de prueba'!$B$2:$B$65,$A4,'Casos de prueba'!$J$2:$J$65,"OK")</f>
+        <f>COUNTIFS('Casos de prueba'!$B$2:$B$200,$A4,'Casos de prueba'!$J$2:$J$200,"OK")</f>
         <v/>
       </c>
       <c r="D4" s="19">
-        <f>COUNTIFS('Casos de prueba'!$B$2:$B$65,$A4,'Casos de prueba'!$J$2:$J$65,"Corrección")</f>
+        <f>COUNTIFS('Casos de prueba'!$B$2:$B$200,$A4,'Casos de prueba'!$J$2:$J$200,"Corrección")</f>
         <v/>
       </c>
       <c r="E4" s="19">
-        <f>COUNTIFS('Casos de prueba'!$B$2:$B$65,$A4,'Casos de prueba'!$J$2:$J$65,"Pendiente")</f>
+        <f>COUNTIFS('Casos de prueba'!$B$2:$B$200,$A4,'Casos de prueba'!$J$2:$J$200,"Pendiente")</f>
         <v/>
       </c>
       <c r="F4" s="19">
-        <f>COUNTIFS('Casos de prueba'!$B$2:$B$65,$A4,'Casos de prueba'!$J$2:$J$65,"No aplica")</f>
+        <f>COUNTIFS('Casos de prueba'!$B$2:$B$200,$A4,'Casos de prueba'!$J$2:$J$200,"No aplica")</f>
         <v/>
       </c>
       <c r="G4" s="19">
@@ -5857,27 +6373,27 @@
     <row r="5" ht="15" customHeight="1" s="12">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>Generador de consecutivos</t>
         </is>
       </c>
       <c r="B5" s="19">
-        <f>COUNTIF('Casos de prueba'!$B$2:$B$65,A5)</f>
+        <f>COUNTIF('Casos de prueba'!$B$2:$B$200,A5)</f>
         <v/>
       </c>
       <c r="C5" s="19">
-        <f>COUNTIFS('Casos de prueba'!$B$2:$B$65,$A5,'Casos de prueba'!$J$2:$J$65,"OK")</f>
+        <f>COUNTIFS('Casos de prueba'!$B$2:$B$200,$A5,'Casos de prueba'!$J$2:$J$200,"OK")</f>
         <v/>
       </c>
       <c r="D5" s="19">
-        <f>COUNTIFS('Casos de prueba'!$B$2:$B$65,$A5,'Casos de prueba'!$J$2:$J$65,"Corrección")</f>
+        <f>COUNTIFS('Casos de prueba'!$B$2:$B$200,$A5,'Casos de prueba'!$J$2:$J$200,"Corrección")</f>
         <v/>
       </c>
       <c r="E5" s="19">
-        <f>COUNTIFS('Casos de prueba'!$B$2:$B$65,$A5,'Casos de prueba'!$J$2:$J$65,"Pendiente")</f>
+        <f>COUNTIFS('Casos de prueba'!$B$2:$B$200,$A5,'Casos de prueba'!$J$2:$J$200,"Pendiente")</f>
         <v/>
       </c>
       <c r="F5" s="19">
-        <f>COUNTIFS('Casos de prueba'!$B$2:$B$65,$A5,'Casos de prueba'!$J$2:$J$65,"No aplica")</f>
+        <f>COUNTIFS('Casos de prueba'!$B$2:$B$200,$A5,'Casos de prueba'!$J$2:$J$200,"No aplica")</f>
         <v/>
       </c>
       <c r="G5" s="19">
